--- a/dados/base_dados/base_mandatosCMTT.xlsx
+++ b/dados/base_dados/base_mandatosCMTT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cloudprodamazhotmail-my.sharepoint.com/personal/giselebarbosa_prefeitura_sp_gov_br/Documents/Documentos/CMTT/Codigo/dados/base_dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3805" documentId="11_00ECA0F5CC4258B7956F15985683A41322DDD907" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{115E0982-0187-4032-87E2-E307A7E37C27}"/>
+  <xr:revisionPtr revIDLastSave="3811" documentId="11_00ECA0F5CC4258B7956F15985683A41322DDD907" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92FCE56F-D0A2-4D6E-A23F-9C6FB0CB1609}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="646" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="646" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2013ago 2014mai" sheetId="9" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4606" uniqueCount="735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4600" uniqueCount="734">
   <si>
     <t>SEGMENTO</t>
   </si>
@@ -2203,9 +2203,6 @@
   </si>
   <si>
     <t>Rafael Del Monaco Drummond Ferreira</t>
-  </si>
-  <si>
-    <t>CARGO_EXTERNO</t>
   </si>
   <si>
     <t>Tatiana Aparecida Galante</t>
@@ -2777,9 +2774,7 @@
       <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
-        <v>718</v>
-      </c>
+      <c r="H1" s="11"/>
       <c r="I1" s="7"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
@@ -11944,9 +11939,7 @@
       <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
-        <v>718</v>
-      </c>
+      <c r="H1" s="11"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
@@ -14345,7 +14338,7 @@
       <c r="B118" s="33"/>
       <c r="C118" s="33"/>
       <c r="D118" s="46" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E118" s="33"/>
       <c r="F118" s="34" t="s">
@@ -18019,9 +18012,7 @@
       <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
-        <v>718</v>
-      </c>
+      <c r="H1" s="11"/>
     </row>
     <row r="2" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
@@ -20204,7 +20195,7 @@
         <v>479</v>
       </c>
       <c r="D111" s="13" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E111" s="11" t="s">
         <v>42</v>
@@ -22769,9 +22760,7 @@
       <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
-        <v>718</v>
-      </c>
+      <c r="H1" s="11"/>
       <c r="I1" s="17"/>
       <c r="J1" s="16"/>
       <c r="K1" s="16"/>
@@ -22908,7 +22897,7 @@
         <v>96</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>42</v>
@@ -22928,7 +22917,7 @@
         <v>96</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>44</v>
@@ -23193,7 +23182,7 @@
         <v>344</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>44</v>
@@ -24730,7 +24719,7 @@
         <v>268</v>
       </c>
       <c r="D105" s="18" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E105" s="11" t="s">
         <v>42</v>
@@ -25024,7 +25013,7 @@
         <v>184</v>
       </c>
       <c r="D121" s="18" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E121" s="11" t="s">
         <v>42</v>
@@ -25044,7 +25033,7 @@
         <v>184</v>
       </c>
       <c r="D122" s="18" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E122" s="10" t="s">
         <v>44</v>
@@ -25221,9 +25210,7 @@
       <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
-        <v>718</v>
-      </c>
+      <c r="H1" s="11"/>
     </row>
     <row r="2" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
@@ -25397,7 +25384,7 @@
         <v>365</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>44</v>
@@ -25488,7 +25475,7 @@
         <v>218</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E15" s="11" t="s">
         <v>42</v>
@@ -25888,7 +25875,7 @@
         <v>379</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E35" s="11" t="s">
         <v>42</v>
@@ -26687,7 +26674,7 @@
         <v>232</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>44</v>
@@ -26786,7 +26773,7 @@
         <v>108</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E82" s="10" t="s">
         <v>44</v>
@@ -26986,7 +26973,7 @@
         <v>340</v>
       </c>
       <c r="D92" s="23" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E92" s="10" t="s">
         <v>44</v>
@@ -27744,9 +27731,7 @@
       <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
-        <v>718</v>
-      </c>
+      <c r="H1" s="11"/>
     </row>
     <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -27840,7 +27825,7 @@
         <v>92</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>44</v>
@@ -27860,7 +27845,7 @@
         <v>92</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>42</v>
@@ -27880,7 +27865,7 @@
         <v>96</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>44</v>
@@ -29470,7 +29455,7 @@
         <v>399</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E89" s="11" t="s">
         <v>44</v>
@@ -29591,7 +29576,7 @@
         <v>340</v>
       </c>
       <c r="D95" s="11" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E95" s="11" t="s">
         <v>44</v>

--- a/dados/base_dados/base_mandatosCMTT.xlsx
+++ b/dados/base_dados/base_mandatosCMTT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cloudprodamazhotmail-my.sharepoint.com/personal/giselebarbosa_prefeitura_sp_gov_br/Documents/Documentos/CMTT/Codigo/dados/base_dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3811" documentId="11_00ECA0F5CC4258B7956F15985683A41322DDD907" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92FCE56F-D0A2-4D6E-A23F-9C6FB0CB1609}"/>
+  <xr:revisionPtr revIDLastSave="3930" documentId="11_00ECA0F5CC4258B7956F15985683A41322DDD907" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD35B100-B3DE-47D0-A5D0-7D18E584DE6D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="646" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="646" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2013ago 2014mai" sheetId="9" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2013ago 2014mai'!$A$1:$G$91</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2014jun 2016ago'!$A$1:$G$119</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2016set 2019mar'!$A$1:$G$196</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2019abr 2022jan'!$A$1:$G$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2019abr 2022jan'!$A$1:$G$143</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2022fev 2024fev'!$A$1:$G$129</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'2024mar 2026jan'!$A$1:$G$132</definedName>
   </definedNames>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4600" uniqueCount="734">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4729" uniqueCount="747">
   <si>
     <t>SEGMENTO</t>
   </si>
@@ -1581,9 +1581,6 @@
     <t>Valmir de Souza</t>
   </si>
   <si>
-    <t>Rafael Calabria</t>
-  </si>
-  <si>
     <t>Maria Lindacy Alves</t>
   </si>
   <si>
@@ -2251,13 +2248,55 @@
   </si>
   <si>
     <t>Priscila de Magalhães Soares Nishino</t>
+  </si>
+  <si>
+    <t>Elisabete França</t>
+  </si>
+  <si>
+    <t>Carlos Eduardo G. de Vasconcellos</t>
+  </si>
+  <si>
+    <t>Eleonora Cordeiro Matoso</t>
+  </si>
+  <si>
+    <t>Heliana Lombardi Artigiani</t>
+  </si>
+  <si>
+    <t>Isabela Muniz</t>
+  </si>
+  <si>
+    <t>Maria Teresa Diniz</t>
+  </si>
+  <si>
+    <t>Renata de Andrade Leal</t>
+  </si>
+  <si>
+    <t>Regina Célia da Silveira Santana</t>
+  </si>
+  <si>
+    <t>Maria Cristina Fernando Biondilo</t>
+  </si>
+  <si>
+    <t>Arlindo Amaro</t>
+  </si>
+  <si>
+    <t>Fábio de Castro Pacini</t>
+  </si>
+  <si>
+    <t>Luciana Delbem</t>
+  </si>
+  <si>
+    <t>Letícia Yoshimoto Simionato</t>
+  </si>
+  <si>
+    <t>Rosângela Sartorelli</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2279,14 +2318,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2399,120 +2447,124 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2530,10 +2582,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4093,7 +4141,7 @@
         <v>131</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D62" s="7" t="s">
         <v>132</v>
@@ -4116,7 +4164,7 @@
         <v>131</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D63" s="7" t="s">
         <v>134</v>
@@ -14234,7 +14282,7 @@
         <v>131</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D112" s="7" t="s">
         <v>132</v>
@@ -14257,7 +14305,7 @@
         <v>131</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D113" s="7" t="s">
         <v>134</v>
@@ -14338,7 +14386,7 @@
       <c r="B118" s="33"/>
       <c r="C118" s="33"/>
       <c r="D118" s="46" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="E118" s="33"/>
       <c r="F118" s="34" t="s">
@@ -18289,7 +18337,7 @@
         <v>365</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>44</v>
@@ -19977,7 +20025,7 @@
         <v>460</v>
       </c>
       <c r="D100" s="13" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="E100" s="10" t="s">
         <v>44</v>
@@ -20195,7 +20243,7 @@
         <v>479</v>
       </c>
       <c r="D111" s="13" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E111" s="11" t="s">
         <v>42</v>
@@ -21484,7 +21532,7 @@
         <v>160</v>
       </c>
       <c r="D175" s="13" t="s">
-        <v>510</v>
+        <v>567</v>
       </c>
       <c r="E175" s="10" t="s">
         <v>44</v>
@@ -21504,7 +21552,7 @@
         <v>287</v>
       </c>
       <c r="D176" s="13" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E176" s="10" t="s">
         <v>44</v>
@@ -21524,7 +21572,7 @@
         <v>287</v>
       </c>
       <c r="D177" s="13" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="E177" s="11" t="s">
         <v>42</v>
@@ -21666,7 +21714,7 @@
         <v>131</v>
       </c>
       <c r="C184" s="7" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D184" s="7" t="s">
         <v>453</v>
@@ -21687,7 +21735,7 @@
         <v>131</v>
       </c>
       <c r="C185" s="7" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D185" s="6" t="s">
         <v>132</v>
@@ -21708,7 +21756,7 @@
         <v>131</v>
       </c>
       <c r="C186" s="7" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D186" s="6" t="s">
         <v>134</v>
@@ -21729,7 +21777,7 @@
         <v>131</v>
       </c>
       <c r="C187" s="7" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D187" s="10" t="s">
         <v>452</v>
@@ -22719,7 +22767,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{785DC0EF-AA30-4942-8459-04093C6F3502}">
-  <dimension ref="A1:M128"/>
+  <dimension ref="A1:M146"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="44" style="10" customWidth="1"/>
@@ -22770,20 +22818,16 @@
         <v>38</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>313</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>192</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="20"/>
       <c r="E2" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F2" s="20" t="s">
-        <v>12</v>
-      </c>
+      <c r="F2" s="20"/>
       <c r="G2" s="10"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
@@ -22791,53 +22835,48 @@
         <v>38</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>313</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>55</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="18"/>
       <c r="E3" s="10" t="s">
         <v>44</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
-        <v>38</v>
+        <v>258</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>315</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>318</v>
+        <v>259</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>561</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F4" s="20" t="s">
+      <c r="F4" s="18" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
-        <v>38</v>
+        <v>258</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>315</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>316</v>
+        <v>259</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>147</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>515</v>
+        <v>219</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>44</v>
@@ -22848,16 +22887,16 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>92</v>
+        <v>241</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>460</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>361</v>
+        <v>544</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>42</v>
@@ -22868,16 +22907,16 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>92</v>
+        <v>241</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>460</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>363</v>
+        <v>545</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>44</v>
@@ -22888,16 +22927,16 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>96</v>
+        <v>241</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>462</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>463</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>721</v>
+        <v>461</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>42</v>
@@ -22908,16 +22947,16 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>96</v>
+        <v>241</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>462</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>463</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>44</v>
@@ -22931,18 +22970,18 @@
         <v>90</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>364</v>
+        <v>91</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>365</v>
+        <v>92</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>527</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="18" t="s">
+        <v>363</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -22951,82 +22990,99 @@
         <v>90</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>364</v>
+        <v>91</v>
       </c>
       <c r="C11" s="47" t="s">
-        <v>365</v>
+        <v>92</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>366</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F11" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="18" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="C12" s="26" t="s">
-        <v>300</v>
-      </c>
-      <c r="D12" s="20"/>
-      <c r="E12" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" s="20"/>
+        <v>90</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="47" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>721</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="C13" s="26" t="s">
-        <v>300</v>
-      </c>
-      <c r="D13" s="18"/>
-      <c r="E13" s="10" t="s">
-        <v>44</v>
+        <v>90</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" s="47" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>720</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="C14" s="36" t="s">
-        <v>384</v>
-      </c>
-      <c r="D14" s="18"/>
+      <c r="B14" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C14" s="47" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>620</v>
+      </c>
       <c r="E14" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="18"/>
-      <c r="M14" s="7"/>
+      <c r="F14" s="18" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="C15" s="36" t="s">
-        <v>384</v>
-      </c>
-      <c r="D15" s="18"/>
+      <c r="B15" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="C15" s="47" t="s">
+        <v>365</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>366</v>
+      </c>
       <c r="E15" s="10" t="s">
         <v>44</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>18</v>
       </c>
       <c r="M15" s="7"/>
     </row>
@@ -23034,479 +23090,471 @@
       <c r="A16" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>422</v>
-      </c>
-      <c r="C16" s="36" t="s">
-        <v>423</v>
+      <c r="B16" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="47" t="s">
+        <v>96</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>538</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F16" s="18" t="s">
-        <v>18</v>
+        <v>743</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="M16" s="7"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>422</v>
-      </c>
-      <c r="C17" s="36" t="s">
-        <v>423</v>
+      <c r="B17" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="C17" s="47" t="s">
+        <v>365</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>539</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>44</v>
+        <v>744</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>42</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="M17" s="7"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="C18" s="47" t="s">
+        <v>365</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>526</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="M18" s="7"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A19" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="C19" s="36" t="s">
+        <v>227</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>740</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="M19" s="7"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A20" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="C20" s="36" t="s">
+        <v>227</v>
+      </c>
+      <c r="D20" s="18"/>
+      <c r="E20" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A21" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D21" s="18"/>
+      <c r="E21" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F21" s="18"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A22" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D22" s="18"/>
+      <c r="E22" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A23" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>728</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A24" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="D24" s="18"/>
+      <c r="E24" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>590</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A26" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="D26" s="18"/>
+      <c r="E26" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A27" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>523</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F18" s="20" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>350</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>524</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>353</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>525</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F20" s="20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>353</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>526</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>343</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F22" s="20" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>343</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>720</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="C24" s="36" t="s">
-        <v>347</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>291</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F24" s="20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="C25" s="36" t="s">
-        <v>347</v>
-      </c>
-      <c r="D25" s="18" t="s">
-        <v>522</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>406</v>
-      </c>
-      <c r="C26" s="36" t="s">
-        <v>124</v>
-      </c>
-      <c r="D26" s="18"/>
-      <c r="E26" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F26" s="18"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>406</v>
-      </c>
-      <c r="C27" s="36" t="s">
-        <v>124</v>
-      </c>
-      <c r="D27" s="18"/>
-      <c r="E27" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B27" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="C27" s="26" t="s">
+        <v>300</v>
+      </c>
+      <c r="D27" s="20"/>
+      <c r="E27" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F27" s="20"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" s="11" t="s">
         <v>38</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>194</v>
+        <v>299</v>
       </c>
       <c r="C28" s="26" t="s">
-        <v>195</v>
-      </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F28" s="20"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+        <v>300</v>
+      </c>
+      <c r="D28" s="18"/>
+      <c r="E28" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" s="11" t="s">
-        <v>38</v>
+        <v>258</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="C29" s="36" t="s">
-        <v>195</v>
-      </c>
-      <c r="D29" s="18"/>
-      <c r="E29" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+        <v>263</v>
+      </c>
+      <c r="C29" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>562</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F29" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" s="11" t="s">
-        <v>38</v>
+        <v>258</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>62</v>
+        <v>263</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F30" s="20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+        <v>264</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" s="11" t="s">
-        <v>38</v>
+        <v>258</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>62</v>
+        <v>267</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>63</v>
+        <v>268</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F31" s="10" t="s">
+        <v>722</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F31" s="18" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="C32" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="D32" s="18"/>
-      <c r="E32" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F32" s="18"/>
+        <v>258</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="C32" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="D32" s="19"/>
+      <c r="E32" s="10" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="C33" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="D33" s="18"/>
+        <v>258</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="C33" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>212</v>
+      </c>
       <c r="E33" s="10" t="s">
         <v>44</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="C34" s="36" t="s">
-        <v>379</v>
-      </c>
-      <c r="D34" s="18"/>
+        <v>258</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="C34" s="26" t="s">
+        <v>272</v>
+      </c>
+      <c r="D34" s="42" t="s">
+        <v>563</v>
+      </c>
       <c r="E34" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F34" s="18"/>
+      <c r="F34" s="18" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="C35" s="36" t="s">
-        <v>379</v>
-      </c>
-      <c r="D35" s="18"/>
-      <c r="E35" s="10" t="s">
-        <v>44</v>
+        <v>258</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>500</v>
+      </c>
+      <c r="C35" s="26" t="s">
+        <v>501</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>502</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F35" s="18" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C36" s="36" t="s">
-        <v>136</v>
-      </c>
-      <c r="D36" s="18" t="s">
-        <v>544</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F36" s="18" t="s">
+        <v>258</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>500</v>
+      </c>
+      <c r="C36" s="26" t="s">
+        <v>501</v>
+      </c>
+      <c r="D36" s="23" t="s">
+        <v>564</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F36" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C37" s="36" t="s">
-        <v>136</v>
-      </c>
-      <c r="D37" s="18" t="s">
-        <v>458</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F37" s="10" t="s">
-        <v>18</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="C37" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="D37" s="19"/>
+      <c r="E37" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F37" s="19"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>198</v>
+        <v>258</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>275</v>
       </c>
       <c r="C38" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="D38" s="18" t="s">
-        <v>70</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="D38" s="19"/>
       <c r="E38" s="10" t="s">
         <v>44</v>
-      </c>
-      <c r="F38" s="10" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="11" t="s">
-        <v>38</v>
+        <v>258</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>67</v>
+        <v>278</v>
       </c>
       <c r="C39" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="D39" s="20" t="s">
-        <v>69</v>
+        <v>184</v>
+      </c>
+      <c r="D39" s="18" t="s">
+        <v>723</v>
       </c>
       <c r="E39" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F39" s="20" t="s">
+      <c r="F39" s="18" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="11" t="s">
-        <v>38</v>
+        <v>258</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>187</v>
+        <v>278</v>
       </c>
       <c r="C40" s="26" t="s">
-        <v>188</v>
-      </c>
-      <c r="D40" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="E40" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F40" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="D40" s="18" t="s">
+        <v>724</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F40" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="11" t="s">
-        <v>38</v>
+        <v>258</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>187</v>
+        <v>280</v>
       </c>
       <c r="C41" s="26" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="D41" s="18" t="s">
-        <v>306</v>
+        <v>566</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>44</v>
@@ -23517,138 +23565,156 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="C42" s="36" t="s">
-        <v>227</v>
-      </c>
-      <c r="D42" s="18"/>
+        <v>258</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="C42" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="D42" s="18" t="s">
+        <v>565</v>
+      </c>
       <c r="E42" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F42" s="18"/>
+      <c r="F42" s="18" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="C43" s="36" t="s">
-        <v>227</v>
-      </c>
-      <c r="D43" s="18"/>
+        <v>258</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="C43" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="D43" s="18" t="s">
+        <v>568</v>
+      </c>
       <c r="E43" s="10" t="s">
         <v>44</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="11" t="s">
-        <v>90</v>
+        <v>258</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>533</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>438</v>
-      </c>
-      <c r="D44" s="18"/>
+        <v>283</v>
+      </c>
+      <c r="C44" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="D44" s="18" t="s">
+        <v>567</v>
+      </c>
       <c r="E44" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F44" s="18"/>
+      <c r="F44" s="18" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="11" t="s">
-        <v>90</v>
+        <v>258</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>533</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>438</v>
-      </c>
-      <c r="D45" s="18"/>
+        <v>286</v>
+      </c>
+      <c r="C45" s="26" t="s">
+        <v>287</v>
+      </c>
+      <c r="D45" s="18" t="s">
+        <v>570</v>
+      </c>
       <c r="E45" s="10" t="s">
         <v>44</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="11" t="s">
-        <v>38</v>
+        <v>258</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="D46" s="20" t="s">
-        <v>200</v>
+        <v>286</v>
+      </c>
+      <c r="C46" s="26" t="s">
+        <v>287</v>
+      </c>
+      <c r="D46" s="18" t="s">
+        <v>569</v>
       </c>
       <c r="E46" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F46" s="20" t="s">
-        <v>12</v>
+      <c r="F46" s="18" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B47" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>324</v>
+        <v>90</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>108</v>
       </c>
       <c r="D47" s="18" t="s">
-        <v>516</v>
-      </c>
-      <c r="E47" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F47" s="10" t="s">
+        <v>737</v>
+      </c>
+      <c r="E47" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F47" s="18" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>326</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="D48" s="20" t="s">
-        <v>517</v>
-      </c>
-      <c r="E48" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F48" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D48" s="18" t="s">
+        <v>741</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F48" s="10" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B49" s="10" t="s">
-        <v>326</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>327</v>
+        <v>90</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>112</v>
       </c>
       <c r="D49" s="18" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="E49" s="10" t="s">
         <v>44</v>
@@ -23657,38 +23723,38 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="10" t="s">
-        <v>307</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="D50" s="20" t="s">
-        <v>514</v>
+        <v>90</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D50" s="18" t="s">
+        <v>527</v>
       </c>
       <c r="E50" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F50" s="20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F50" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B51" s="10" t="s">
-        <v>307</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>308</v>
+        <v>90</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>399</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>57</v>
+        <v>529</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>44</v>
@@ -23697,58 +23763,58 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="10" t="s">
-        <v>309</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="D52" s="20" t="s">
-        <v>311</v>
-      </c>
-      <c r="E52" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F52" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="D52" s="18" t="s">
+        <v>623</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F52" s="10" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="10" t="s">
-        <v>309</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>310</v>
+        <v>90</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>399</v>
       </c>
       <c r="D53" s="18" t="s">
-        <v>312</v>
-      </c>
-      <c r="E53" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F53" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="E53" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F53" s="18" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="B54" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>116</v>
+      <c r="B54" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>399</v>
       </c>
       <c r="D54" s="18" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E54" s="11" t="s">
         <v>42</v>
@@ -23757,218 +23823,212 @@
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" s="11" t="s">
         <v>90</v>
       </c>
       <c r="B55" s="7" t="s">
+        <v>530</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="D55" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F55" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>530</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="D56" s="18" t="s">
+        <v>531</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F56" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="D57" s="18" t="s">
+        <v>746</v>
+      </c>
+      <c r="E57" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F57" s="18"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="D58" s="18"/>
+      <c r="E58" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="D59" s="18" t="s">
+        <v>738</v>
+      </c>
+      <c r="E59" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G59" s="11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="A60" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>733</v>
+      </c>
+      <c r="E60" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F60" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="G60" s="11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A61" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D61" s="18" t="s">
+        <v>739</v>
+      </c>
+      <c r="E61" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F61" s="18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A62" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D62" s="18"/>
+      <c r="E62" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A63" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B63" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C63" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="D55" s="18" t="s">
-        <v>410</v>
-      </c>
-      <c r="E55" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F55" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A56" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>540</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="D56" s="18" t="s">
-        <v>541</v>
-      </c>
-      <c r="E56" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F56" s="18" t="s">
+      <c r="D63" s="18" t="s">
+        <v>408</v>
+      </c>
+      <c r="E63" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F63" s="18" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A57" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>540</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="D57" s="18" t="s">
-        <v>453</v>
-      </c>
-      <c r="E57" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F57" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A58" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="B58" s="10" t="s">
-        <v>459</v>
-      </c>
-      <c r="C58" s="10" t="s">
-        <v>460</v>
-      </c>
-      <c r="D58" s="18" t="s">
-        <v>545</v>
-      </c>
-      <c r="E58" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F58" s="18" t="s">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A64" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D64" s="18" t="s">
+        <v>595</v>
+      </c>
+      <c r="E64" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F64" s="18" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A59" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="B59" s="10" t="s">
-        <v>459</v>
-      </c>
-      <c r="C59" s="10" t="s">
-        <v>460</v>
-      </c>
-      <c r="D59" s="18" t="s">
-        <v>546</v>
-      </c>
-      <c r="E59" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F59" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A60" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="B60" s="10" t="s">
-        <v>462</v>
-      </c>
-      <c r="C60" s="10" t="s">
-        <v>463</v>
-      </c>
-      <c r="D60" s="18" t="s">
-        <v>461</v>
-      </c>
-      <c r="E60" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F60" s="18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A61" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="B61" s="10" t="s">
-        <v>462</v>
-      </c>
-      <c r="C61" s="10" t="s">
-        <v>463</v>
-      </c>
-      <c r="D61" s="18" t="s">
-        <v>717</v>
-      </c>
-      <c r="E61" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F61" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A62" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="B62" s="10" t="s">
-        <v>465</v>
-      </c>
-      <c r="C62" s="10" t="s">
-        <v>466</v>
-      </c>
-      <c r="D62" s="18" t="s">
-        <v>547</v>
-      </c>
-      <c r="E62" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F62" s="18" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A63" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="B63" s="10" t="s">
-        <v>465</v>
-      </c>
-      <c r="C63" s="10" t="s">
-        <v>466</v>
-      </c>
-      <c r="D63" s="18" t="s">
-        <v>548</v>
-      </c>
-      <c r="E63" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F63" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A64" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="B64" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="C64" s="10" t="s">
-        <v>469</v>
-      </c>
-      <c r="D64" s="18" t="s">
-        <v>549</v>
-      </c>
-      <c r="E64" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F64" s="18" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="B65" s="10" t="s">
-        <v>468</v>
-      </c>
-      <c r="C65" s="10" t="s">
-        <v>469</v>
+        <v>90</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>116</v>
       </c>
       <c r="D65" s="18" t="s">
-        <v>550</v>
+        <v>410</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>44</v>
@@ -23979,242 +24039,233 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" s="11" t="s">
-        <v>241</v>
+        <v>90</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>471</v>
+        <v>411</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>472</v>
-      </c>
-      <c r="D66" s="18" t="s">
-        <v>551</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="D66" s="19"/>
       <c r="E66" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F66" s="18" t="s">
-        <v>18</v>
-      </c>
+      <c r="F66" s="19"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" s="11" t="s">
-        <v>241</v>
+        <v>90</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>471</v>
+        <v>411</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>472</v>
-      </c>
-      <c r="D67" s="18" t="s">
-        <v>552</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="D67" s="19"/>
       <c r="E67" s="10" t="s">
         <v>44</v>
-      </c>
-      <c r="F67" s="10" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" s="11" t="s">
-        <v>241</v>
+        <v>90</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>474</v>
+        <v>533</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>475</v>
-      </c>
-      <c r="D68" s="42" t="s">
-        <v>553</v>
+        <v>120</v>
+      </c>
+      <c r="D68" s="18" t="s">
+        <v>534</v>
       </c>
       <c r="E68" s="11" t="s">
         <v>42</v>
       </c>
       <c r="F68" s="18" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" s="11" t="s">
-        <v>241</v>
+        <v>90</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>474</v>
+        <v>533</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>475</v>
+        <v>120</v>
       </c>
       <c r="D69" s="18" t="s">
-        <v>554</v>
+        <v>535</v>
       </c>
       <c r="E69" s="10" t="s">
         <v>44</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" s="11" t="s">
-        <v>241</v>
+        <v>90</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>478</v>
+        <v>418</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>479</v>
+        <v>419</v>
       </c>
       <c r="D70" s="18" t="s">
-        <v>555</v>
+        <v>455</v>
       </c>
       <c r="E70" s="11" t="s">
         <v>42</v>
       </c>
       <c r="F70" s="18" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" s="11" t="s">
-        <v>241</v>
+        <v>90</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>478</v>
+        <v>418</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>479</v>
+        <v>419</v>
       </c>
       <c r="D71" s="18" t="s">
-        <v>604</v>
-      </c>
-      <c r="E71" s="10" t="s">
-        <v>44</v>
+        <v>736</v>
+      </c>
+      <c r="E71" s="11" t="s">
+        <v>42</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="11" t="s">
-        <v>241</v>
+        <v>90</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>481</v>
+        <v>418</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>482</v>
+        <v>419</v>
       </c>
       <c r="D72" s="18" t="s">
-        <v>556</v>
-      </c>
-      <c r="E72" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F72" s="18" t="s">
-        <v>12</v>
+        <v>536</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F72" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="B73" s="10" t="s">
-        <v>481</v>
-      </c>
-      <c r="C73" s="10" t="s">
-        <v>482</v>
+        <v>90</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>423</v>
       </c>
       <c r="D73" s="18" t="s">
-        <v>557</v>
+        <v>538</v>
       </c>
       <c r="E73" s="10" t="s">
         <v>44</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="B74" s="10" t="s">
-        <v>485</v>
-      </c>
-      <c r="C74" s="10" t="s">
-        <v>486</v>
+        <v>90</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>423</v>
       </c>
       <c r="D74" s="18" t="s">
-        <v>558</v>
-      </c>
-      <c r="E74" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F74" s="18" t="s">
-        <v>12</v>
+        <v>735</v>
+      </c>
+      <c r="E74" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="F74" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="B75" s="10" t="s">
-        <v>485</v>
-      </c>
-      <c r="C75" s="10" t="s">
-        <v>486</v>
+        <v>90</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>423</v>
       </c>
       <c r="D75" s="18" t="s">
-        <v>559</v>
-      </c>
-      <c r="E75" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F75" s="10" t="s">
-        <v>12</v>
+        <v>537</v>
+      </c>
+      <c r="E75" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F75" s="18" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="B76" s="10" t="s">
-        <v>489</v>
-      </c>
-      <c r="C76" s="10" t="s">
-        <v>490</v>
+        <v>90</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>128</v>
       </c>
       <c r="D76" s="18" t="s">
-        <v>560</v>
-      </c>
-      <c r="E76" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F76" s="18" t="s">
+        <v>453</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F76" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="B77" s="10" t="s">
-        <v>489</v>
-      </c>
-      <c r="C77" s="10" t="s">
-        <v>490</v>
-      </c>
-      <c r="D77" s="18" t="s">
-        <v>561</v>
+        <v>90</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D77" s="49" t="s">
+        <v>745</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
@@ -24222,134 +24273,161 @@
         <v>90</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>232</v>
+        <v>128</v>
       </c>
       <c r="D78" s="18" t="s">
-        <v>436</v>
+        <v>540</v>
       </c>
       <c r="E78" s="11" t="s">
         <v>42</v>
       </c>
       <c r="F78" s="18" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A79" s="11" t="s">
-        <v>90</v>
-      </c>
+      <c r="A79" s="11"/>
       <c r="B79" s="7" t="s">
-        <v>531</v>
+        <v>131</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>232</v>
+        <v>714</v>
       </c>
       <c r="D79" s="18" t="s">
-        <v>532</v>
+        <v>599</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>44</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="B80" s="10" t="s">
-        <v>411</v>
-      </c>
-      <c r="C80" s="10" t="s">
-        <v>412</v>
-      </c>
-      <c r="D80" s="19"/>
-      <c r="E80" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F80" s="19"/>
+      <c r="B80" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>714</v>
+      </c>
+      <c r="D80" s="18" t="s">
+        <v>542</v>
+      </c>
+      <c r="E80" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F80" s="10" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="B81" s="10" t="s">
-        <v>411</v>
-      </c>
-      <c r="C81" s="10" t="s">
-        <v>412</v>
-      </c>
-      <c r="D81" s="19"/>
-      <c r="E81" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="A82" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="B82" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="C82" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="D82" s="11"/>
+      <c r="B81" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>714</v>
+      </c>
+      <c r="D81" s="18" t="s">
+        <v>733</v>
+      </c>
+      <c r="E81" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F81" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G81" s="10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A82" s="11"/>
+      <c r="B82" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>714</v>
+      </c>
+      <c r="D82" s="18" t="s">
+        <v>632</v>
+      </c>
       <c r="E82" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F82" s="5"/>
-      <c r="G82" s="11" t="s">
-        <v>87</v>
+      <c r="F82" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G82" s="10" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="B83" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="C83" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="D83" s="18"/>
+      <c r="B83" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>714</v>
+      </c>
+      <c r="D83" s="18" t="s">
+        <v>403</v>
+      </c>
       <c r="E83" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F83" s="18"/>
+      <c r="F83" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G83" s="10" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="B84" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="C84" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="D84" s="18"/>
-      <c r="E84" s="10" t="s">
-        <v>44</v>
+      <c r="B84" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>714</v>
+      </c>
+      <c r="D84" s="18" t="s">
+        <v>541</v>
+      </c>
+      <c r="E84" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F84" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G84" s="10" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="B85" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="C85" s="9" t="s">
-        <v>112</v>
+      <c r="B85" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>136</v>
       </c>
       <c r="D85" s="18" t="s">
-        <v>528</v>
+        <v>543</v>
       </c>
       <c r="E85" s="11" t="s">
         <v>42</v>
@@ -24362,19 +24440,19 @@
       <c r="A86" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="B86" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="C86" s="9" t="s">
-        <v>112</v>
+      <c r="B86" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>136</v>
       </c>
       <c r="D86" s="18" t="s">
-        <v>529</v>
-      </c>
-      <c r="E86" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F86" s="10" t="s">
+        <v>734</v>
+      </c>
+      <c r="E86" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F86" s="18" t="s">
         <v>12</v>
       </c>
     </row>
@@ -24382,80 +24460,75 @@
       <c r="A87" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="B87" s="9" t="s">
-        <v>398</v>
-      </c>
-      <c r="C87" s="9" t="s">
-        <v>399</v>
+      <c r="B87" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>136</v>
       </c>
       <c r="D87" s="18" t="s">
-        <v>404</v>
-      </c>
-      <c r="E87" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F87" s="18" t="s">
+        <v>458</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F87" s="10" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B88" s="9" t="s">
-        <v>398</v>
-      </c>
-      <c r="C88" s="9" t="s">
-        <v>399</v>
-      </c>
-      <c r="D88" s="18" t="s">
-        <v>530</v>
-      </c>
-      <c r="E88" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F88" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B88" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="C88" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="D88" s="20" t="s">
+        <v>512</v>
+      </c>
+      <c r="E88" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F88" s="20" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" s="11" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>534</v>
+        <v>301</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="D89" s="18" t="s">
-        <v>535</v>
-      </c>
-      <c r="E89" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F89" s="18" t="s">
-        <v>12</v>
+        <v>302</v>
+      </c>
+      <c r="D89" s="19"/>
+      <c r="E89" s="10" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" s="11" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>534</v>
+        <v>187</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="D90" s="18" t="s">
-        <v>536</v>
-      </c>
-      <c r="E90" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F90" s="10" t="s">
-        <v>18</v>
+        <v>188</v>
+      </c>
+      <c r="D90" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="E90" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F90" s="20" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.2">
@@ -24463,30 +24536,39 @@
         <v>38</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="C91" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="D91" s="20"/>
-      <c r="E91" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F91" s="20"/>
+        <v>187</v>
+      </c>
+      <c r="C91" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="D91" s="18" t="s">
+        <v>306</v>
+      </c>
+      <c r="E91" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F91" s="10" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" s="11" t="s">
         <v>38</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>337</v>
+        <v>307</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="D92" s="18"/>
+        <v>308</v>
+      </c>
+      <c r="D92" s="18" t="s">
+        <v>57</v>
+      </c>
       <c r="E92" s="10" t="s">
         <v>44</v>
+      </c>
+      <c r="F92" s="10" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.2">
@@ -24494,13 +24576,19 @@
         <v>38</v>
       </c>
       <c r="B93" s="10" t="s">
-        <v>339</v>
+        <v>307</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>340</v>
+        <v>308</v>
+      </c>
+      <c r="D93" s="20" t="s">
+        <v>513</v>
       </c>
       <c r="E93" s="11" t="s">
         <v>42</v>
+      </c>
+      <c r="F93" s="20" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.2">
@@ -24508,13 +24596,19 @@
         <v>38</v>
       </c>
       <c r="B94" s="10" t="s">
-        <v>339</v>
+        <v>309</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="E94" s="10" t="s">
-        <v>44</v>
+        <v>310</v>
+      </c>
+      <c r="D94" s="20" t="s">
+        <v>311</v>
+      </c>
+      <c r="E94" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F94" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.2">
@@ -24522,19 +24616,19 @@
         <v>38</v>
       </c>
       <c r="B95" s="10" t="s">
-        <v>331</v>
+        <v>309</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="D95" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E95" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F95" s="20" t="s">
-        <v>12</v>
+        <v>310</v>
+      </c>
+      <c r="D95" s="18" t="s">
+        <v>312</v>
+      </c>
+      <c r="E95" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F95" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.2">
@@ -24542,13 +24636,13 @@
         <v>38</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="D96" s="18" t="s">
-        <v>519</v>
+        <v>55</v>
       </c>
       <c r="E96" s="10" t="s">
         <v>44</v>
@@ -24562,19 +24656,19 @@
         <v>38</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>334</v>
+        <v>314</v>
       </c>
       <c r="D97" s="20" t="s">
-        <v>520</v>
+        <v>192</v>
       </c>
       <c r="E97" s="11" t="s">
         <v>42</v>
       </c>
       <c r="F97" s="20" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
@@ -24582,13 +24676,13 @@
         <v>38</v>
       </c>
       <c r="B98" s="10" t="s">
-        <v>333</v>
+        <v>315</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>334</v>
+        <v>316</v>
       </c>
       <c r="D98" s="18" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="E98" s="10" t="s">
         <v>44</v>
@@ -24602,219 +24696,233 @@
         <v>38</v>
       </c>
       <c r="B99" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C99" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D99" s="20"/>
+        <v>315</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D99" s="20" t="s">
+        <v>318</v>
+      </c>
       <c r="E99" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F99" s="20"/>
+      <c r="F99" s="20" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="11" t="s">
         <v>38</v>
       </c>
       <c r="B100" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C100" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D100" s="18"/>
-      <c r="E100" s="10" t="s">
-        <v>44</v>
+        <v>315</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="D100" s="23" t="s">
+        <v>613</v>
+      </c>
+      <c r="E100" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F100" s="37" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A101" s="11" t="s">
-        <v>258</v>
+      <c r="A101" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="B101" s="10" t="s">
-        <v>259</v>
+        <v>315</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="D101" s="18" t="s">
-        <v>562</v>
-      </c>
-      <c r="E101" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F101" s="18" t="s">
-        <v>18</v>
+        <v>316</v>
+      </c>
+      <c r="D101" s="10" t="s">
+        <v>574</v>
+      </c>
+      <c r="E101" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F101" s="10" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="11" t="s">
-        <v>258</v>
+        <v>38</v>
       </c>
       <c r="B102" s="10" t="s">
-        <v>259</v>
+        <v>62</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="D102" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="E102" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F102" s="10" t="s">
-        <v>18</v>
+        <v>63</v>
+      </c>
+      <c r="D102" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="E102" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F102" s="20" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="11" t="s">
-        <v>258</v>
+        <v>38</v>
       </c>
       <c r="B103" s="10" t="s">
-        <v>263</v>
+        <v>62</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>264</v>
+        <v>63</v>
       </c>
       <c r="D103" s="18" t="s">
-        <v>563</v>
-      </c>
-      <c r="E103" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F103" s="18" t="s">
-        <v>12</v>
+        <v>319</v>
+      </c>
+      <c r="E103" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F103" s="10" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="11" t="s">
-        <v>258</v>
+        <v>38</v>
       </c>
       <c r="B104" s="10" t="s">
-        <v>263</v>
+        <v>194</v>
       </c>
       <c r="C104" s="10" t="s">
-        <v>264</v>
-      </c>
-      <c r="D104" s="10" t="s">
-        <v>495</v>
-      </c>
-      <c r="E104" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F104" s="10" t="s">
-        <v>18</v>
+        <v>195</v>
+      </c>
+      <c r="D104" s="20" t="s">
+        <v>614</v>
+      </c>
+      <c r="E104" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F104" s="20" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" s="11" t="s">
-        <v>258</v>
+        <v>38</v>
       </c>
       <c r="B105" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="C105" s="10" t="s">
-        <v>268</v>
+        <v>194</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>195</v>
       </c>
       <c r="D105" s="18" t="s">
-        <v>723</v>
-      </c>
-      <c r="E105" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F105" s="18" t="s">
-        <v>18</v>
+        <v>575</v>
+      </c>
+      <c r="E105" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F105" s="10" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="B106" s="10" t="s">
-        <v>267</v>
+        <v>38</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>198</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="D106" s="19"/>
+        <v>68</v>
+      </c>
+      <c r="D106" s="18" t="s">
+        <v>70</v>
+      </c>
       <c r="E106" s="10" t="s">
         <v>44</v>
+      </c>
+      <c r="F106" s="10" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" s="11" t="s">
-        <v>258</v>
+        <v>38</v>
       </c>
       <c r="B107" s="10" t="s">
-        <v>271</v>
+        <v>67</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="D107" s="42" t="s">
-        <v>564</v>
+        <v>68</v>
+      </c>
+      <c r="D107" s="20" t="s">
+        <v>69</v>
       </c>
       <c r="E107" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F107" s="18" t="s">
-        <v>18</v>
+      <c r="F107" s="20" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="11" t="s">
-        <v>258</v>
+        <v>38</v>
       </c>
       <c r="B108" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="C108" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="D108" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="E108" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F108" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="D108" s="20" t="s">
+        <v>200</v>
+      </c>
+      <c r="E108" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F108" s="20" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" s="11" t="s">
-        <v>258</v>
+        <v>38</v>
       </c>
       <c r="B109" s="10" t="s">
-        <v>500</v>
-      </c>
-      <c r="C109" s="10" t="s">
-        <v>501</v>
+        <v>323</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>324</v>
       </c>
       <c r="D109" s="18" t="s">
-        <v>502</v>
-      </c>
-      <c r="E109" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F109" s="18" t="s">
+        <v>515</v>
+      </c>
+      <c r="E109" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F109" s="10" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" s="11" t="s">
-        <v>258</v>
+        <v>38</v>
       </c>
       <c r="B110" s="10" t="s">
-        <v>500</v>
-      </c>
-      <c r="C110" s="10" t="s">
-        <v>501</v>
-      </c>
-      <c r="D110" s="23" t="s">
-        <v>565</v>
+        <v>326</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="D110" s="18" t="s">
+        <v>517</v>
       </c>
       <c r="E110" s="10" t="s">
         <v>44</v>
@@ -24825,169 +24933,164 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="11" t="s">
-        <v>258</v>
+        <v>38</v>
       </c>
       <c r="B111" s="10" t="s">
-        <v>280</v>
-      </c>
-      <c r="C111" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="D111" s="18" t="s">
-        <v>566</v>
+        <v>326</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="D111" s="20" t="s">
+        <v>516</v>
       </c>
       <c r="E111" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F111" s="18" t="s">
-        <v>12</v>
+      <c r="F111" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" s="11" t="s">
-        <v>258</v>
+        <v>38</v>
       </c>
       <c r="B112" s="10" t="s">
-        <v>280</v>
-      </c>
-      <c r="C112" s="10" t="s">
-        <v>157</v>
+        <v>331</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>332</v>
       </c>
       <c r="D112" s="18" t="s">
-        <v>567</v>
+        <v>518</v>
       </c>
       <c r="E112" s="10" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F112" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="11" t="s">
-        <v>258</v>
+        <v>38</v>
       </c>
       <c r="B113" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="C113" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="D113" s="18" t="s">
-        <v>568</v>
+        <v>331</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="D113" s="6" t="s">
+        <v>76</v>
       </c>
       <c r="E113" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F113" s="18" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F113" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" s="11" t="s">
-        <v>258</v>
+        <v>38</v>
       </c>
       <c r="B114" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="C114" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="D114" s="18" t="s">
-        <v>569</v>
-      </c>
-      <c r="E114" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F114" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="D114" s="20" t="s">
+        <v>519</v>
+      </c>
+      <c r="E114" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F114" s="20" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="11" t="s">
-        <v>258</v>
+        <v>38</v>
       </c>
       <c r="B115" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="C115" s="10" t="s">
-        <v>287</v>
+        <v>333</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>334</v>
       </c>
       <c r="D115" s="18" t="s">
-        <v>570</v>
-      </c>
-      <c r="E115" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F115" s="18" t="s">
+        <v>520</v>
+      </c>
+      <c r="E115" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F115" s="10" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="11" t="s">
-        <v>258</v>
+        <v>38</v>
       </c>
       <c r="B116" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="C116" s="10" t="s">
-        <v>287</v>
-      </c>
-      <c r="D116" s="18" t="s">
-        <v>571</v>
-      </c>
-      <c r="E116" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F116" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
+        <v>337</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D116" s="20"/>
+      <c r="E116" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F116" s="20"/>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" s="11" t="s">
-        <v>258</v>
+        <v>38</v>
       </c>
       <c r="B117" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="C117" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="D117" s="19"/>
-      <c r="E117" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F117" s="19"/>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
+        <v>337</v>
+      </c>
+      <c r="C117" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D117" s="18"/>
+      <c r="E117" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" s="11" t="s">
-        <v>258</v>
+        <v>38</v>
       </c>
       <c r="B118" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="C118" s="10" t="s">
-        <v>181</v>
-      </c>
-      <c r="D118" s="19"/>
-      <c r="E118" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
+        <v>339</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E118" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" s="11" t="s">
-        <v>258</v>
+        <v>38</v>
       </c>
       <c r="B119" s="10" t="s">
-        <v>290</v>
-      </c>
-      <c r="C119" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="D119" s="19"/>
-      <c r="E119" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F119" s="19"/>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
+        <v>339</v>
+      </c>
+      <c r="C119" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E119" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" s="11" t="s">
         <v>258</v>
       </c>
@@ -24998,160 +25101,158 @@
         <v>165</v>
       </c>
       <c r="D120" s="19"/>
-      <c r="E120" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E120" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F120" s="19"/>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" s="11" t="s">
         <v>258</v>
       </c>
       <c r="B121" s="10" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="D121" s="18" t="s">
-        <v>724</v>
-      </c>
-      <c r="E121" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F121" s="18" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
+        <v>165</v>
+      </c>
+      <c r="D121" s="19"/>
+      <c r="E121" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" s="11" t="s">
-        <v>258</v>
+        <v>38</v>
       </c>
       <c r="B122" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="C122" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="D122" s="18" t="s">
-        <v>725</v>
-      </c>
-      <c r="E122" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F122" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
+        <v>343</v>
+      </c>
+      <c r="C122" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="D122" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="E122" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F122" s="20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B123" s="7" t="s">
-        <v>131</v>
+        <v>38</v>
+      </c>
+      <c r="B123" s="10" t="s">
+        <v>343</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>715</v>
+        <v>344</v>
       </c>
       <c r="D123" s="18" t="s">
-        <v>542</v>
-      </c>
-      <c r="E123" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F123" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G123" s="10" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
+        <v>719</v>
+      </c>
+      <c r="E123" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F123" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B124" s="7" t="s">
-        <v>131</v>
+        <v>38</v>
+      </c>
+      <c r="B124" s="10" t="s">
+        <v>346</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>715</v>
-      </c>
-      <c r="D124" s="18" t="s">
-        <v>543</v>
-      </c>
-      <c r="E124" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F124" s="10" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
+        <v>347</v>
+      </c>
+      <c r="D124" s="20" t="s">
+        <v>291</v>
+      </c>
+      <c r="E124" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F124" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" s="11" t="s">
         <v>38</v>
       </c>
       <c r="B125" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="C125" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="D125" s="20" t="s">
-        <v>513</v>
-      </c>
-      <c r="E125" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F125" s="20" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
+        <v>346</v>
+      </c>
+      <c r="C125" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="D125" s="18" t="s">
+        <v>521</v>
+      </c>
+      <c r="E125" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F125" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" s="11" t="s">
         <v>38</v>
       </c>
       <c r="B126" s="10" t="s">
-        <v>301</v>
-      </c>
-      <c r="C126" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="D126" s="19"/>
+        <v>350</v>
+      </c>
+      <c r="C126" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="D126" s="18" t="s">
+        <v>523</v>
+      </c>
       <c r="E126" s="10" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F126" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" s="11" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="B127" s="10" t="s">
-        <v>418</v>
-      </c>
-      <c r="C127" s="10" t="s">
-        <v>419</v>
-      </c>
-      <c r="D127" s="18" t="s">
-        <v>455</v>
+        <v>350</v>
+      </c>
+      <c r="C127" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="D127" s="20" t="s">
+        <v>522</v>
       </c>
       <c r="E127" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="F127" s="18" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F127" s="20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" s="11" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="B128" s="10" t="s">
-        <v>418</v>
-      </c>
-      <c r="C128" s="10" t="s">
-        <v>419</v>
+        <v>353</v>
+      </c>
+      <c r="C128" s="7" t="s">
+        <v>354</v>
       </c>
       <c r="D128" s="18" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="E128" s="10" t="s">
         <v>44</v>
@@ -25160,10 +25261,368 @@
         <v>18</v>
       </c>
     </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A129" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B129" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="C129" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="D129" s="20" t="s">
+        <v>524</v>
+      </c>
+      <c r="E129" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F129" s="20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A130" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="B130" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="C130" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="D130" s="18" t="s">
+        <v>546</v>
+      </c>
+      <c r="E130" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F130" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A131" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="B131" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="C131" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="D131" s="18" t="s">
+        <v>547</v>
+      </c>
+      <c r="E131" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F131" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A132" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="B132" s="10" t="s">
+        <v>468</v>
+      </c>
+      <c r="C132" s="10" t="s">
+        <v>469</v>
+      </c>
+      <c r="D132" s="18" t="s">
+        <v>549</v>
+      </c>
+      <c r="E132" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F132" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A133" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="B133" s="10" t="s">
+        <v>468</v>
+      </c>
+      <c r="C133" s="10" t="s">
+        <v>469</v>
+      </c>
+      <c r="D133" s="18" t="s">
+        <v>548</v>
+      </c>
+      <c r="E133" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F133" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A134" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="B134" s="10" t="s">
+        <v>471</v>
+      </c>
+      <c r="C134" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="D134" s="18" t="s">
+        <v>551</v>
+      </c>
+      <c r="E134" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F134" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A135" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="B135" s="10" t="s">
+        <v>471</v>
+      </c>
+      <c r="C135" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="D135" s="18" t="s">
+        <v>550</v>
+      </c>
+      <c r="E135" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F135" s="18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A136" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="B136" s="10" t="s">
+        <v>474</v>
+      </c>
+      <c r="C136" s="10" t="s">
+        <v>475</v>
+      </c>
+      <c r="D136" s="42" t="s">
+        <v>552</v>
+      </c>
+      <c r="E136" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F136" s="18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A137" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="B137" s="10" t="s">
+        <v>474</v>
+      </c>
+      <c r="C137" s="10" t="s">
+        <v>475</v>
+      </c>
+      <c r="D137" s="18" t="s">
+        <v>553</v>
+      </c>
+      <c r="E137" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F137" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A138" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="B138" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="C138" s="10" t="s">
+        <v>479</v>
+      </c>
+      <c r="D138" s="18" t="s">
+        <v>554</v>
+      </c>
+      <c r="E138" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F138" s="18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A139" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="B139" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="C139" s="10" t="s">
+        <v>479</v>
+      </c>
+      <c r="D139" s="18" t="s">
+        <v>603</v>
+      </c>
+      <c r="E139" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F139" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A140" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="B140" s="10" t="s">
+        <v>481</v>
+      </c>
+      <c r="C140" s="10" t="s">
+        <v>482</v>
+      </c>
+      <c r="D140" s="18" t="s">
+        <v>555</v>
+      </c>
+      <c r="E140" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F140" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A141" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="B141" s="10" t="s">
+        <v>481</v>
+      </c>
+      <c r="C141" s="10" t="s">
+        <v>482</v>
+      </c>
+      <c r="D141" s="18" t="s">
+        <v>556</v>
+      </c>
+      <c r="E141" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F141" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A142" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="B142" s="10" t="s">
+        <v>485</v>
+      </c>
+      <c r="C142" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="D142" s="18" t="s">
+        <v>557</v>
+      </c>
+      <c r="E142" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F142" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A143" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="B143" s="10" t="s">
+        <v>485</v>
+      </c>
+      <c r="C143" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="D143" s="18" t="s">
+        <v>558</v>
+      </c>
+      <c r="E143" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F143" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A144" s="11"/>
+      <c r="B144" s="10" t="s">
+        <v>485</v>
+      </c>
+      <c r="C144" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="D144" s="18" t="s">
+        <v>742</v>
+      </c>
+      <c r="E144" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F144" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A145" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="B145" s="10" t="s">
+        <v>489</v>
+      </c>
+      <c r="C145" s="10" t="s">
+        <v>490</v>
+      </c>
+      <c r="D145" s="18" t="s">
+        <v>560</v>
+      </c>
+      <c r="E145" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F145" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A146" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="B146" s="10" t="s">
+        <v>489</v>
+      </c>
+      <c r="C146" s="10" t="s">
+        <v>490</v>
+      </c>
+      <c r="D146" s="18" t="s">
+        <v>559</v>
+      </c>
+      <c r="E146" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F146" s="18" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G128" xr:uid="{785DC0EF-AA30-4942-8459-04093C6F3502}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G128">
-      <sortCondition ref="C1:C128"/>
+  <autoFilter ref="A1:G143" xr:uid="{785DC0EF-AA30-4942-8459-04093C6F3502}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G145">
+      <sortCondition ref="B1:B143"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -25244,7 +25703,7 @@
         <v>314</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="E3" s="11" t="s">
         <v>42</v>
@@ -25264,7 +25723,7 @@
         <v>316</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>44</v>
@@ -25284,7 +25743,7 @@
         <v>316</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>42</v>
@@ -25304,7 +25763,7 @@
         <v>92</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>44</v>
@@ -25324,7 +25783,7 @@
         <v>92</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>42</v>
@@ -25344,7 +25803,7 @@
         <v>96</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>44</v>
@@ -25384,7 +25843,7 @@
         <v>365</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>44</v>
@@ -25404,7 +25863,7 @@
         <v>365</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>42</v>
@@ -25449,13 +25908,13 @@
         <v>90</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C14" s="36" t="s">
         <v>218</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>44</v>
@@ -25469,13 +25928,13 @@
         <v>90</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C15" s="36" t="s">
         <v>218</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="E15" s="11" t="s">
         <v>42</v>
@@ -25495,7 +25954,7 @@
         <v>423</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>44</v>
@@ -25515,7 +25974,7 @@
         <v>423</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E17" s="11" t="s">
         <v>42</v>
@@ -25535,7 +25994,7 @@
         <v>351</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E18" s="10" t="s">
         <v>44</v>
@@ -25555,7 +26014,7 @@
         <v>351</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>42</v>
@@ -25575,7 +26034,7 @@
         <v>354</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E20" s="10" t="s">
         <v>44</v>
@@ -25595,7 +26054,7 @@
         <v>354</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E21" s="11" t="s">
         <v>42</v>
@@ -25655,7 +26114,7 @@
         <v>347</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>44</v>
@@ -25675,7 +26134,7 @@
         <v>347</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>42</v>
@@ -25695,7 +26154,7 @@
         <v>124</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>44</v>
@@ -25715,7 +26174,7 @@
         <v>124</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="E27" s="11" t="s">
         <v>42</v>
@@ -25735,7 +26194,7 @@
         <v>195</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>44</v>
@@ -25755,7 +26214,7 @@
         <v>195</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E29" s="11" t="s">
         <v>42</v>
@@ -25809,13 +26268,13 @@
         <v>90</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>104</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>44</v>
@@ -25829,13 +26288,13 @@
         <v>90</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>104</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E33" s="11" t="s">
         <v>42</v>
@@ -25855,7 +26314,7 @@
         <v>379</v>
       </c>
       <c r="D34" s="23" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>44</v>
@@ -25875,7 +26334,7 @@
         <v>379</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E35" s="11" t="s">
         <v>42</v>
@@ -25895,7 +26354,7 @@
         <v>136</v>
       </c>
       <c r="D36" s="23" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>44</v>
@@ -25915,7 +26374,7 @@
         <v>136</v>
       </c>
       <c r="D37" s="23" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E37" s="11" t="s">
         <v>42</v>
@@ -25935,7 +26394,7 @@
         <v>68</v>
       </c>
       <c r="D38" s="23" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>44</v>
@@ -25975,7 +26434,7 @@
         <v>188</v>
       </c>
       <c r="D40" s="23" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>44</v>
@@ -26015,7 +26474,7 @@
         <v>227</v>
       </c>
       <c r="D42" s="23" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>44</v>
@@ -26035,7 +26494,7 @@
         <v>227</v>
       </c>
       <c r="D43" s="23" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="E43" s="11" t="s">
         <v>42</v>
@@ -26049,13 +26508,13 @@
         <v>90</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C44" s="10" t="s">
         <v>438</v>
       </c>
       <c r="D44" s="23" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E44" s="10" t="s">
         <v>44</v>
@@ -26069,13 +26528,13 @@
         <v>90</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C45" s="10" t="s">
         <v>438</v>
       </c>
       <c r="D45" s="23" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E45" s="11" t="s">
         <v>42</v>
@@ -26095,7 +26554,7 @@
         <v>324</v>
       </c>
       <c r="D46" s="23" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E46" s="10" t="s">
         <v>44</v>
@@ -26135,7 +26594,7 @@
         <v>327</v>
       </c>
       <c r="D48" s="23" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E48" s="10" t="s">
         <v>44</v>
@@ -26155,7 +26614,7 @@
         <v>327</v>
       </c>
       <c r="D49" s="23" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E49" s="11" t="s">
         <v>42</v>
@@ -26195,7 +26654,7 @@
         <v>308</v>
       </c>
       <c r="D51" s="23" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E51" s="11" t="s">
         <v>42</v>
@@ -26215,7 +26674,7 @@
         <v>310</v>
       </c>
       <c r="D52" s="23" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E52" s="10" t="s">
         <v>44</v>
@@ -26235,7 +26694,7 @@
         <v>310</v>
       </c>
       <c r="D53" s="23" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="E53" s="11" t="s">
         <v>42</v>
@@ -26255,7 +26714,7 @@
         <v>116</v>
       </c>
       <c r="D54" s="23" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E54" s="10" t="s">
         <v>44</v>
@@ -26275,7 +26734,7 @@
         <v>116</v>
       </c>
       <c r="D55" s="23" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E55" s="11" t="s">
         <v>42</v>
@@ -26295,7 +26754,7 @@
         <v>460</v>
       </c>
       <c r="D56" s="23" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E56" s="10" t="s">
         <v>44</v>
@@ -26315,7 +26774,7 @@
         <v>460</v>
       </c>
       <c r="D57" s="23" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="E57" s="11" t="s">
         <v>42</v>
@@ -26350,7 +26809,7 @@
         <v>463</v>
       </c>
       <c r="D59" s="23" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E59" s="11" t="s">
         <v>42</v>
@@ -26385,7 +26844,7 @@
         <v>466</v>
       </c>
       <c r="D61" s="23" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E61" s="11" t="s">
         <v>42</v>
@@ -26420,7 +26879,7 @@
         <v>469</v>
       </c>
       <c r="D63" s="23" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="E63" s="11" t="s">
         <v>42</v>
@@ -26455,7 +26914,7 @@
         <v>472</v>
       </c>
       <c r="D65" s="23" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E65" s="11" t="s">
         <v>42</v>
@@ -26508,7 +26967,7 @@
         <v>479</v>
       </c>
       <c r="D68" s="23" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E68" s="10" t="s">
         <v>44</v>
@@ -26528,7 +26987,7 @@
         <v>479</v>
       </c>
       <c r="D69" s="23" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E69" s="11" t="s">
         <v>42</v>
@@ -26548,7 +27007,7 @@
         <v>482</v>
       </c>
       <c r="D70" s="23" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E70" s="10" t="s">
         <v>44</v>
@@ -26568,7 +27027,7 @@
         <v>482</v>
       </c>
       <c r="D71" s="23" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>44</v>
@@ -26588,7 +27047,7 @@
         <v>482</v>
       </c>
       <c r="D72" s="23" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="E72" s="11" t="s">
         <v>42</v>
@@ -26623,7 +27082,7 @@
         <v>486</v>
       </c>
       <c r="D74" s="23" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="E74" s="11" t="s">
         <v>42</v>
@@ -26668,13 +27127,13 @@
         <v>90</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C77" s="7" t="s">
         <v>232</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>44</v>
@@ -26688,13 +27147,13 @@
         <v>90</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C78" s="7" t="s">
         <v>232</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E78" s="11" t="s">
         <v>42</v>
@@ -26714,7 +27173,7 @@
         <v>412</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E79" s="10" t="s">
         <v>44</v>
@@ -26734,7 +27193,7 @@
         <v>412</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="E80" s="11" t="s">
         <v>42</v>
@@ -26773,7 +27232,7 @@
         <v>108</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E82" s="10" t="s">
         <v>44</v>
@@ -26793,7 +27252,7 @@
         <v>108</v>
       </c>
       <c r="D83" s="23" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E83" s="11" t="s">
         <v>42</v>
@@ -26813,7 +27272,7 @@
         <v>112</v>
       </c>
       <c r="D84" s="23" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E84" s="10" t="s">
         <v>44</v>
@@ -26833,7 +27292,7 @@
         <v>112</v>
       </c>
       <c r="D85" s="23" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E85" s="11" t="s">
         <v>42</v>
@@ -26887,13 +27346,13 @@
         <v>90</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C88" s="10" t="s">
         <v>120</v>
       </c>
       <c r="D88" s="23" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E88" s="10" t="s">
         <v>44</v>
@@ -26907,13 +27366,13 @@
         <v>90</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C89" s="10" t="s">
         <v>120</v>
       </c>
       <c r="D89" s="23" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="E89" s="11" t="s">
         <v>42</v>
@@ -26933,7 +27392,7 @@
         <v>338</v>
       </c>
       <c r="D90" s="23" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E90" s="10" t="s">
         <v>44</v>
@@ -26953,7 +27412,7 @@
         <v>338</v>
       </c>
       <c r="D91" s="23" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E91" s="11" t="s">
         <v>42</v>
@@ -26973,7 +27432,7 @@
         <v>340</v>
       </c>
       <c r="D92" s="23" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E92" s="10" t="s">
         <v>44</v>
@@ -26993,7 +27452,7 @@
         <v>340</v>
       </c>
       <c r="D93" s="23" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E93" s="11" t="s">
         <v>42</v>
@@ -27013,7 +27472,7 @@
         <v>332</v>
       </c>
       <c r="D94" s="23" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E94" s="10" t="s">
         <v>44</v>
@@ -27033,7 +27492,7 @@
         <v>332</v>
       </c>
       <c r="D95" s="23" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E95" s="11" t="s">
         <v>42</v>
@@ -27053,7 +27512,7 @@
         <v>334</v>
       </c>
       <c r="D96" s="23" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E96" s="10" t="s">
         <v>44</v>
@@ -27073,7 +27532,7 @@
         <v>334</v>
       </c>
       <c r="D97" s="23" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="E97" s="11" t="s">
         <v>42</v>
@@ -27133,7 +27592,7 @@
         <v>147</v>
       </c>
       <c r="D100" s="23" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="E100" s="10" t="s">
         <v>44</v>
@@ -27153,7 +27612,7 @@
         <v>147</v>
       </c>
       <c r="D101" s="23" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="E101" s="11" t="s">
         <v>42</v>
@@ -27219,7 +27678,7 @@
         <v>268</v>
       </c>
       <c r="D105" s="23" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E105" s="11" t="s">
         <v>42</v>
@@ -27239,7 +27698,7 @@
         <v>272</v>
       </c>
       <c r="D106" s="23" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E106" s="10" t="s">
         <v>44</v>
@@ -27259,7 +27718,7 @@
         <v>272</v>
       </c>
       <c r="D107" s="23" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="E107" s="11" t="s">
         <v>42</v>
@@ -27279,7 +27738,7 @@
         <v>501</v>
       </c>
       <c r="D108" s="23" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E108" s="10" t="s">
         <v>44</v>
@@ -27299,7 +27758,7 @@
         <v>501</v>
       </c>
       <c r="D109" s="23" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="E109" s="11" t="s">
         <v>42</v>
@@ -27365,7 +27824,7 @@
         <v>160</v>
       </c>
       <c r="D113" s="23" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="E113" s="11" t="s">
         <v>42</v>
@@ -27385,7 +27844,7 @@
         <v>287</v>
       </c>
       <c r="D114" s="23" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="E114" s="10" t="s">
         <v>44</v>
@@ -27405,7 +27864,7 @@
         <v>287</v>
       </c>
       <c r="D115" s="23" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E115" s="11" t="s">
         <v>42</v>
@@ -27425,7 +27884,7 @@
         <v>181</v>
       </c>
       <c r="D116" s="23" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="E116" s="10" t="s">
         <v>44</v>
@@ -27445,7 +27904,7 @@
         <v>181</v>
       </c>
       <c r="D117" s="23" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E117" s="11" t="s">
         <v>42</v>
@@ -27480,7 +27939,7 @@
         <v>165</v>
       </c>
       <c r="D119" s="23" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E119" s="11" t="s">
         <v>42</v>
@@ -27500,7 +27959,7 @@
         <v>184</v>
       </c>
       <c r="D120" s="23" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="E120" s="10" t="s">
         <v>44</v>
@@ -27520,7 +27979,7 @@
         <v>184</v>
       </c>
       <c r="D121" s="23" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E121" s="11" t="s">
         <v>42</v>
@@ -27534,13 +27993,13 @@
         <v>90</v>
       </c>
       <c r="B122" s="7" t="s">
+        <v>598</v>
+      </c>
+      <c r="C122" s="7" t="s">
+        <v>714</v>
+      </c>
+      <c r="D122" s="23" t="s">
         <v>599</v>
-      </c>
-      <c r="C122" s="7" t="s">
-        <v>715</v>
-      </c>
-      <c r="D122" s="23" t="s">
-        <v>600</v>
       </c>
       <c r="E122" s="10" t="s">
         <v>44</v>
@@ -27554,13 +28013,13 @@
         <v>90</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D123" s="23" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E123" s="11" t="s">
         <v>42</v>
@@ -27577,13 +28036,13 @@
         <v>90</v>
       </c>
       <c r="B124" s="7" t="s">
+        <v>592</v>
+      </c>
+      <c r="C124" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="D124" s="23" t="s">
         <v>593</v>
-      </c>
-      <c r="C124" s="7" t="s">
-        <v>716</v>
-      </c>
-      <c r="D124" s="23" t="s">
-        <v>594</v>
       </c>
       <c r="E124" s="10" t="s">
         <v>44</v>
@@ -27598,13 +28057,13 @@
         <v>90</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D125" s="23" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="E125" s="11" t="s">
         <v>42</v>
@@ -27624,7 +28083,7 @@
         <v>302</v>
       </c>
       <c r="D126" s="23" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E126" s="10" t="s">
         <v>44</v>
@@ -27644,7 +28103,7 @@
         <v>302</v>
       </c>
       <c r="D127" s="23" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E127" s="11" t="s">
         <v>42</v>
@@ -27658,7 +28117,7 @@
         <v>90</v>
       </c>
       <c r="B128" s="10" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C128" s="10" t="s">
         <v>419</v>
@@ -27673,7 +28132,7 @@
         <v>90</v>
       </c>
       <c r="B129" s="10" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C129" s="10" t="s">
         <v>419</v>
@@ -27744,7 +28203,7 @@
         <v>314</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E2" s="11" t="s">
         <v>44</v>
@@ -27765,7 +28224,7 @@
         <v>314</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E3" s="11" t="s">
         <v>42</v>
@@ -27805,7 +28264,7 @@
         <v>316</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>42</v>
@@ -27825,7 +28284,7 @@
         <v>92</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>44</v>
@@ -27845,7 +28304,7 @@
         <v>92</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>42</v>
@@ -27865,7 +28324,7 @@
         <v>96</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>44</v>
@@ -27885,7 +28344,7 @@
         <v>96</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>42</v>
@@ -27963,13 +28422,13 @@
         <v>90</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C14" s="36" t="s">
         <v>218</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="E14" s="11" t="s">
         <v>44</v>
@@ -27983,13 +28442,13 @@
         <v>90</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C15" s="36" t="s">
         <v>218</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="E15" s="11" t="s">
         <v>42</v>
@@ -28009,7 +28468,7 @@
         <v>423</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E16" s="11" t="s">
         <v>44</v>
@@ -28029,7 +28488,7 @@
         <v>423</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="E17" s="11" t="s">
         <v>42</v>
@@ -28049,7 +28508,7 @@
         <v>351</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E18" s="11" t="s">
         <v>44</v>
@@ -28069,7 +28528,7 @@
         <v>351</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E19" s="11" t="s">
         <v>42</v>
@@ -28089,7 +28548,7 @@
         <v>354</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>44</v>
@@ -28109,7 +28568,7 @@
         <v>354</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E21" s="11" t="s">
         <v>42</v>
@@ -28129,7 +28588,7 @@
         <v>344</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E22" s="11" t="s">
         <v>44</v>
@@ -28189,7 +28648,7 @@
         <v>347</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>42</v>
@@ -28203,13 +28662,13 @@
         <v>90</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C26" s="26" t="s">
+        <v>666</v>
+      </c>
+      <c r="D26" s="11" t="s">
         <v>667</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>668</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>44</v>
@@ -28226,10 +28685,10 @@
         <v>411</v>
       </c>
       <c r="C27" s="26" t="s">
+        <v>675</v>
+      </c>
+      <c r="D27" s="11" t="s">
         <v>676</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>677</v>
       </c>
       <c r="E27" s="11" t="s">
         <v>44</v>
@@ -28243,13 +28702,13 @@
         <v>90</v>
       </c>
       <c r="B28" s="11" t="s">
+        <v>653</v>
+      </c>
+      <c r="C28" s="44" t="s">
         <v>654</v>
       </c>
-      <c r="C28" s="44" t="s">
+      <c r="D28" s="11" t="s">
         <v>655</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>656</v>
       </c>
       <c r="E28" s="11" t="s">
         <v>44</v>
@@ -28263,13 +28722,13 @@
         <v>90</v>
       </c>
       <c r="B29" s="11" t="s">
+        <v>653</v>
+      </c>
+      <c r="C29" s="44" t="s">
         <v>654</v>
       </c>
-      <c r="C29" s="44" t="s">
-        <v>655</v>
-      </c>
       <c r="D29" s="11" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E29" s="11" t="s">
         <v>42</v>
@@ -28292,7 +28751,7 @@
         <v>124</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="E30" s="11" t="s">
         <v>44</v>
@@ -28312,7 +28771,7 @@
         <v>124</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="E31" s="11" t="s">
         <v>42</v>
@@ -28332,7 +28791,7 @@
         <v>195</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E32" s="11" t="s">
         <v>44</v>
@@ -28352,7 +28811,7 @@
         <v>195</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E33" s="11" t="s">
         <v>42</v>
@@ -28406,13 +28865,13 @@
         <v>90</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C36" s="36" t="s">
         <v>104</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E36" s="11" t="s">
         <v>44</v>
@@ -28426,13 +28885,13 @@
         <v>90</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C37" s="36" t="s">
         <v>104</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E37" s="11" t="s">
         <v>42</v>
@@ -28452,7 +28911,7 @@
         <v>379</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E38" s="11" t="s">
         <v>44</v>
@@ -28472,7 +28931,7 @@
         <v>379</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E39" s="11" t="s">
         <v>42</v>
@@ -28492,7 +28951,7 @@
         <v>136</v>
       </c>
       <c r="D40" s="23" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E40" s="11" t="s">
         <v>44</v>
@@ -28512,7 +28971,7 @@
         <v>136</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E41" s="11" t="s">
         <v>42</v>
@@ -28552,7 +29011,7 @@
         <v>68</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E43" s="11" t="s">
         <v>42</v>
@@ -28572,7 +29031,7 @@
         <v>188</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E44" s="11" t="s">
         <v>44</v>
@@ -28612,7 +29071,7 @@
         <v>227</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="E46" s="11" t="s">
         <v>44</v>
@@ -28632,7 +29091,7 @@
         <v>227</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E47" s="11" t="s">
         <v>42</v>
@@ -28646,13 +29105,13 @@
         <v>90</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C48" s="10" t="s">
         <v>438</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="E48" s="11" t="s">
         <v>44</v>
@@ -28666,13 +29125,13 @@
         <v>90</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C49" s="10" t="s">
         <v>438</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E49" s="11" t="s">
         <v>42</v>
@@ -28692,7 +29151,7 @@
         <v>324</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E50" s="11" t="s">
         <v>44</v>
@@ -28764,7 +29223,7 @@
         <v>308</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E54" s="11" t="s">
         <v>44</v>
@@ -28824,7 +29283,7 @@
         <v>310</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="E57" s="11" t="s">
         <v>42</v>
@@ -28844,7 +29303,7 @@
         <v>116</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="E58" s="11" t="s">
         <v>44</v>
@@ -28864,7 +29323,7 @@
         <v>116</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="E59" s="11" t="s">
         <v>42</v>
@@ -28884,7 +29343,7 @@
         <v>460</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E60" s="11" t="s">
         <v>44</v>
@@ -28904,7 +29363,7 @@
         <v>460</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E61" s="11" t="s">
         <v>42</v>
@@ -28924,7 +29383,7 @@
         <v>463</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E62" s="11" t="s">
         <v>44</v>
@@ -28944,7 +29403,7 @@
         <v>463</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E63" s="11" t="s">
         <v>42</v>
@@ -28964,7 +29423,7 @@
         <v>466</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="E64" s="11" t="s">
         <v>44</v>
@@ -28984,7 +29443,7 @@
         <v>466</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E65" s="11" t="s">
         <v>42</v>
@@ -29004,7 +29463,7 @@
         <v>469</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E66" s="11" t="s">
         <v>44</v>
@@ -29024,7 +29483,7 @@
         <v>469</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E67" s="11" t="s">
         <v>42</v>
@@ -29044,7 +29503,7 @@
         <v>472</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E68" s="11" t="s">
         <v>44</v>
@@ -29064,7 +29523,7 @@
         <v>472</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E69" s="11" t="s">
         <v>42</v>
@@ -29100,7 +29559,7 @@
         <v>475</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E71" s="11" t="s">
         <v>42</v>
@@ -29120,7 +29579,7 @@
         <v>479</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="E72" s="11" t="s">
         <v>44</v>
@@ -29140,7 +29599,7 @@
         <v>479</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E73" s="11" t="s">
         <v>42</v>
@@ -29160,7 +29619,7 @@
         <v>482</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="E74" s="11" t="s">
         <v>44</v>
@@ -29180,7 +29639,7 @@
         <v>482</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E75" s="11" t="s">
         <v>42</v>
@@ -29216,7 +29675,7 @@
         <v>486</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="E77" s="11" t="s">
         <v>42</v>
@@ -29252,7 +29711,7 @@
         <v>490</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E79" s="11" t="s">
         <v>42</v>
@@ -29266,13 +29725,13 @@
         <v>90</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C80" s="7" t="s">
         <v>232</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="E80" s="11" t="s">
         <v>44</v>
@@ -29286,13 +29745,13 @@
         <v>90</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C81" s="7" t="s">
         <v>232</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="E81" s="11" t="s">
         <v>42</v>
@@ -29312,7 +29771,7 @@
         <v>412</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E82" s="11" t="s">
         <v>44</v>
@@ -29332,7 +29791,7 @@
         <v>412</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="E83" s="11" t="s">
         <v>42</v>
@@ -29352,7 +29811,7 @@
         <v>143</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E84" s="11" t="s">
         <v>42</v>
@@ -29375,7 +29834,7 @@
         <v>108</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="E85" s="11" t="s">
         <v>44</v>
@@ -29395,7 +29854,7 @@
         <v>108</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E86" s="11" t="s">
         <v>42</v>
@@ -29415,7 +29874,7 @@
         <v>112</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E87" s="11" t="s">
         <v>44</v>
@@ -29435,7 +29894,7 @@
         <v>112</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E88" s="11" t="s">
         <v>42</v>
@@ -29455,7 +29914,7 @@
         <v>399</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E89" s="11" t="s">
         <v>44</v>
@@ -29475,7 +29934,7 @@
         <v>399</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E90" s="11" t="s">
         <v>42</v>
@@ -29490,13 +29949,13 @@
         <v>90</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C91" s="10" t="s">
         <v>120</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E91" s="11" t="s">
         <v>44</v>
@@ -29510,13 +29969,13 @@
         <v>90</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C92" s="10" t="s">
         <v>120</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E92" s="11" t="s">
         <v>42</v>
@@ -29536,7 +29995,7 @@
         <v>338</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E93" s="11" t="s">
         <v>44</v>
@@ -29556,7 +30015,7 @@
         <v>338</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E94" s="11" t="s">
         <v>42</v>
@@ -29576,7 +30035,7 @@
         <v>340</v>
       </c>
       <c r="D95" s="11" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E95" s="11" t="s">
         <v>44</v>
@@ -29596,7 +30055,7 @@
         <v>340</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="E96" s="11" t="s">
         <v>42</v>
@@ -29616,7 +30075,7 @@
         <v>332</v>
       </c>
       <c r="D97" s="11" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E97" s="11" t="s">
         <v>44</v>
@@ -29636,7 +30095,7 @@
         <v>332</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E98" s="11" t="s">
         <v>42</v>
@@ -29656,7 +30115,7 @@
         <v>334</v>
       </c>
       <c r="D99" s="11" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="E99" s="11" t="s">
         <v>44</v>
@@ -29676,7 +30135,7 @@
         <v>334</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E100" s="11" t="s">
         <v>42</v>
@@ -29736,7 +30195,7 @@
         <v>147</v>
       </c>
       <c r="D103" s="11" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="E103" s="11" t="s">
         <v>44</v>
@@ -29756,7 +30215,7 @@
         <v>147</v>
       </c>
       <c r="D104" s="11" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="E104" s="11" t="s">
         <v>42</v>
@@ -29792,7 +30251,7 @@
         <v>264</v>
       </c>
       <c r="D106" s="11" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E106" s="11" t="s">
         <v>42</v>
@@ -29812,7 +30271,7 @@
         <v>268</v>
       </c>
       <c r="D107" s="11" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E107" s="11" t="s">
         <v>44</v>
@@ -29832,7 +30291,7 @@
         <v>268</v>
       </c>
       <c r="D108" s="11" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E108" s="11" t="s">
         <v>42</v>
@@ -29852,7 +30311,7 @@
         <v>272</v>
       </c>
       <c r="D109" s="11" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E109" s="11" t="s">
         <v>44</v>
@@ -29872,7 +30331,7 @@
         <v>272</v>
       </c>
       <c r="D110" s="11" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="E110" s="11" t="s">
         <v>42</v>
@@ -29892,7 +30351,7 @@
         <v>501</v>
       </c>
       <c r="D111" s="11" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="E111" s="11" t="s">
         <v>44</v>
@@ -29912,7 +30371,7 @@
         <v>501</v>
       </c>
       <c r="D112" s="11" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E112" s="11" t="s">
         <v>42</v>
@@ -29932,7 +30391,7 @@
         <v>157</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="E113" s="11" t="s">
         <v>44</v>
@@ -29988,7 +30447,7 @@
         <v>160</v>
       </c>
       <c r="D116" s="11" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E116" s="11" t="s">
         <v>42</v>
@@ -30008,7 +30467,7 @@
         <v>287</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E117" s="11" t="s">
         <v>44</v>
@@ -30028,7 +30487,7 @@
         <v>287</v>
       </c>
       <c r="D118" s="11" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="E118" s="11" t="s">
         <v>42</v>
@@ -30080,7 +30539,7 @@
         <v>165</v>
       </c>
       <c r="D121" s="11" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E121" s="11" t="s">
         <v>44</v>
@@ -30100,7 +30559,7 @@
         <v>165</v>
       </c>
       <c r="D122" s="11" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="E122" s="11" t="s">
         <v>42</v>
@@ -30136,7 +30595,7 @@
         <v>184</v>
       </c>
       <c r="D124" s="11" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="E124" s="11" t="s">
         <v>42</v>
@@ -30150,13 +30609,13 @@
         <v>90</v>
       </c>
       <c r="B125" s="11" t="s">
+        <v>682</v>
+      </c>
+      <c r="C125" s="11" t="s">
+        <v>714</v>
+      </c>
+      <c r="D125" s="11" t="s">
         <v>683</v>
-      </c>
-      <c r="C125" s="11" t="s">
-        <v>715</v>
-      </c>
-      <c r="D125" s="11" t="s">
-        <v>684</v>
       </c>
       <c r="E125" s="11" t="s">
         <v>44</v>
@@ -30170,13 +30629,13 @@
         <v>90</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C126" s="11" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D126" s="11" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E126" s="11" t="s">
         <v>42</v>
@@ -30190,10 +30649,10 @@
         <v>90</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C127" s="11" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D127" s="11"/>
       <c r="E127" s="11" t="s">
@@ -30206,10 +30665,10 @@
         <v>90</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C128" s="11" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D128" s="11"/>
       <c r="E128" s="11" t="s">
@@ -30228,7 +30687,7 @@
         <v>302</v>
       </c>
       <c r="D129" s="11" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E129" s="11" t="s">
         <v>44</v>
@@ -30248,7 +30707,7 @@
         <v>302</v>
       </c>
       <c r="D130" s="11" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E130" s="11" t="s">
         <v>42</v>
@@ -30262,13 +30721,13 @@
         <v>90</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C131" s="10" t="s">
         <v>419</v>
       </c>
       <c r="D131" s="11" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E131" s="11" t="s">
         <v>44</v>
@@ -30282,13 +30741,13 @@
         <v>90</v>
       </c>
       <c r="B132" s="10" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C132" s="10" t="s">
         <v>419</v>
       </c>
       <c r="D132" s="11" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E132" s="11" t="s">
         <v>42</v>

--- a/dados/base_dados/base_mandatosCMTT.xlsx
+++ b/dados/base_dados/base_mandatosCMTT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cloudprodamazhotmail-my.sharepoint.com/personal/giselebarbosa_prefeitura_sp_gov_br/Documents/Documentos/CMTT/Codigo/dados/base_dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4060" documentId="11_00ECA0F5CC4258B7956F15985683A41322DDD907" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E0A1785-8D56-4884-80A0-EA6616415620}"/>
+  <xr:revisionPtr revIDLastSave="4061" documentId="11_00ECA0F5CC4258B7956F15985683A41322DDD907" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0EEFF18-1770-48A4-A5CA-1BD02DB9D76B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="646" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="646" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2013ago 2014mai" sheetId="9" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4764" uniqueCount="722">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4765" uniqueCount="722">
   <si>
     <t>SEGMENTO</t>
   </si>
@@ -2367,7 +2367,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2482,20 +2482,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -24937,7 +24925,9 @@
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A110" s="10"/>
+      <c r="A110" s="10" t="s">
+        <v>89</v>
+      </c>
       <c r="B110" s="6" t="s">
         <v>127</v>
       </c>
@@ -25866,7 +25856,7 @@
       <c r="B13" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="C13" s="48" t="s">
+      <c r="C13" s="47" t="s">
         <v>105</v>
       </c>
       <c r="D13" s="22" t="s">
@@ -25886,7 +25876,7 @@
       <c r="B14" s="9" t="s">
         <v>317</v>
       </c>
-      <c r="C14" s="49" t="s">
+      <c r="C14" s="34" t="s">
         <v>318</v>
       </c>
       <c r="D14" s="22" t="s">
@@ -25906,7 +25896,7 @@
       <c r="B15" s="9" t="s">
         <v>461</v>
       </c>
-      <c r="C15" s="50" t="s">
+      <c r="C15" s="25" t="s">
         <v>462</v>
       </c>
       <c r="D15" s="22" t="s">
@@ -25929,7 +25919,7 @@
       <c r="B16" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="C16" s="50" t="s">
+      <c r="C16" s="25" t="s">
         <v>142</v>
       </c>
       <c r="D16" s="22" t="s">
@@ -25949,7 +25939,7 @@
       <c r="B17" s="9" t="s">
         <v>288</v>
       </c>
-      <c r="C17" s="50" t="s">
+      <c r="C17" s="25" t="s">
         <v>289</v>
       </c>
       <c r="D17" s="22" t="s">
@@ -28212,7 +28202,7 @@
       <c r="E2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F2" s="53" t="s">
+      <c r="F2" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G2" s="12"/>
@@ -28233,7 +28223,7 @@
       <c r="E3" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F3" s="53" t="s">
+      <c r="F3" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G3" s="1"/>
@@ -28254,7 +28244,7 @@
       <c r="E4" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F4" s="53" t="s">
+      <c r="F4" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G4" s="1"/>
@@ -28275,7 +28265,7 @@
       <c r="E5" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="53" t="s">
+      <c r="F5" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G5" s="1"/>
@@ -28296,7 +28286,7 @@
       <c r="E6" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="53" t="s">
+      <c r="F6" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G6" s="1"/>
@@ -28317,10 +28307,10 @@
       <c r="E7" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="53" t="s">
+      <c r="F7" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="54"/>
+      <c r="G7" s="1"/>
     </row>
     <row r="8" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
@@ -28338,7 +28328,7 @@
       <c r="E8" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F8" s="53" t="s">
+      <c r="F8" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G8" s="1"/>
@@ -28359,7 +28349,7 @@
       <c r="E9" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="53" t="s">
+      <c r="F9" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G9" s="1"/>
@@ -28371,7 +28361,7 @@
       <c r="B10" s="12" t="s">
         <v>461</v>
       </c>
-      <c r="C10" s="54" t="s">
+      <c r="C10" s="1" t="s">
         <v>462</v>
       </c>
       <c r="D10" s="10" t="s">
@@ -28380,7 +28370,7 @@
       <c r="E10" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="53" t="s">
+      <c r="F10" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G10" s="1"/>
@@ -28392,7 +28382,7 @@
       <c r="B11" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="C11" s="52" t="s">
+      <c r="C11" s="3" t="s">
         <v>330</v>
       </c>
       <c r="D11" s="10" t="s">
@@ -28401,7 +28391,7 @@
       <c r="E11" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="53" t="s">
+      <c r="F11" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G11" s="1"/>
@@ -28413,7 +28403,7 @@
       <c r="B12" s="12" t="s">
         <v>511</v>
       </c>
-      <c r="C12" s="54" t="s">
+      <c r="C12" s="1" t="s">
         <v>639</v>
       </c>
       <c r="D12" s="10" t="s">
@@ -28422,7 +28412,7 @@
       <c r="E12" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F12" s="53" t="s">
+      <c r="F12" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G12" s="1"/>
@@ -28434,7 +28424,7 @@
       <c r="B13" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="C13" s="55" t="s">
+      <c r="C13" s="49" t="s">
         <v>105</v>
       </c>
       <c r="D13" s="10" t="s">
@@ -28443,7 +28433,7 @@
       <c r="E13" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="53" t="s">
+      <c r="F13" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G13" s="1"/>
@@ -28455,7 +28445,7 @@
       <c r="B14" s="5" t="s">
         <v>509</v>
       </c>
-      <c r="C14" s="52" t="s">
+      <c r="C14" s="3" t="s">
         <v>219</v>
       </c>
       <c r="D14" s="10" t="s">
@@ -28464,7 +28454,7 @@
       <c r="E14" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F14" s="53" t="s">
+      <c r="F14" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G14" s="1"/>
@@ -28476,16 +28466,16 @@
       <c r="B15" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="C15" s="52" t="s">
+      <c r="C15" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="D15" s="52" t="s">
+      <c r="D15" s="3" t="s">
         <v>76</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="53" t="s">
+      <c r="F15" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G15" s="1"/>
@@ -28497,7 +28487,7 @@
       <c r="B16" s="12" t="s">
         <v>309</v>
       </c>
-      <c r="C16" s="52" t="s">
+      <c r="C16" s="3" t="s">
         <v>310</v>
       </c>
       <c r="D16" s="10" t="s">
@@ -28506,7 +28496,7 @@
       <c r="E16" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="53" t="s">
+      <c r="F16" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G16" s="1"/>
@@ -28518,7 +28508,7 @@
       <c r="B17" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="C17" s="54" t="s">
+      <c r="C17" s="1" t="s">
         <v>289</v>
       </c>
       <c r="D17" s="10" t="s">
@@ -28527,7 +28517,7 @@
       <c r="E17" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F17" s="53" t="s">
+      <c r="F17" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G17" s="1"/>
@@ -28548,7 +28538,7 @@
       <c r="E18" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F18" s="53" t="s">
+      <c r="F18" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G18" s="1"/>
@@ -28569,7 +28559,7 @@
       <c r="E19" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F19" s="53" t="s">
+      <c r="F19" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G19" s="1"/>
@@ -28590,7 +28580,7 @@
       <c r="E20" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F20" s="53" t="s">
+      <c r="F20" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G20" s="1"/>
@@ -28611,7 +28601,7 @@
       <c r="E21" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F21" s="53" t="s">
+      <c r="F21" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G21" s="1"/>
@@ -28623,7 +28613,7 @@
       <c r="B22" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="C22" s="56" t="s">
+      <c r="C22" s="50" t="s">
         <v>91</v>
       </c>
       <c r="D22" s="17" t="s">
@@ -28632,7 +28622,7 @@
       <c r="E22" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F22" s="53" t="s">
+      <c r="F22" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G22" s="1"/>
@@ -28653,7 +28643,7 @@
       <c r="E23" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F23" s="53" t="s">
+      <c r="F23" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G23" s="1"/>
@@ -28665,7 +28655,7 @@
       <c r="B24" s="12" t="s">
         <v>451</v>
       </c>
-      <c r="C24" s="54" t="s">
+      <c r="C24" s="1" t="s">
         <v>452</v>
       </c>
       <c r="D24" s="10" t="s">
@@ -28674,7 +28664,7 @@
       <c r="E24" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F24" s="53" t="s">
+      <c r="F24" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G24" s="1"/>
@@ -28686,7 +28676,7 @@
       <c r="B25" s="12" t="s">
         <v>302</v>
       </c>
-      <c r="C25" s="52" t="s">
+      <c r="C25" s="3" t="s">
         <v>303</v>
       </c>
       <c r="D25" s="10" t="s">
@@ -28695,7 +28685,7 @@
       <c r="E25" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F25" s="53" t="s">
+      <c r="F25" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G25" s="1"/>
@@ -28707,7 +28697,7 @@
       <c r="B26" s="12" t="s">
         <v>573</v>
       </c>
-      <c r="C26" s="54" t="s">
+      <c r="C26" s="1" t="s">
         <v>678</v>
       </c>
       <c r="D26" s="10" t="s">
@@ -28716,7 +28706,7 @@
       <c r="E26" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F26" s="53" t="s">
+      <c r="F26" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G26" s="1" t="s">
@@ -28739,7 +28729,7 @@
       <c r="E27" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F27" s="53" t="s">
+      <c r="F27" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G27" s="1" t="s">
@@ -28762,7 +28752,7 @@
       <c r="E28" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F28" s="53" t="s">
+      <c r="F28" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G28" s="1"/>
@@ -28774,7 +28764,7 @@
       <c r="B29" s="5" t="s">
         <v>391</v>
       </c>
-      <c r="C29" s="52" t="s">
+      <c r="C29" s="3" t="s">
         <v>120</v>
       </c>
       <c r="D29" s="10" t="s">
@@ -28783,7 +28773,7 @@
       <c r="E29" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F29" s="53" t="s">
+      <c r="F29" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G29" s="1"/>
@@ -28804,7 +28794,7 @@
       <c r="E30" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F30" s="53" t="s">
+      <c r="F30" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G30" s="1"/>
@@ -28816,7 +28806,7 @@
       <c r="B31" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="C31" s="54" t="s">
+      <c r="C31" s="1" t="s">
         <v>138</v>
       </c>
       <c r="D31" s="10" t="s">
@@ -28825,7 +28815,7 @@
       <c r="E31" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F31" s="53" t="s">
+      <c r="F31" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G31" s="42" t="s">
@@ -28839,7 +28829,7 @@
       <c r="B32" s="12" t="s">
         <v>396</v>
       </c>
-      <c r="C32" s="54" t="s">
+      <c r="C32" s="1" t="s">
         <v>397</v>
       </c>
       <c r="D32" s="10" t="s">
@@ -28848,7 +28838,7 @@
       <c r="E32" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F32" s="53" t="s">
+      <c r="F32" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G32" s="1"/>
@@ -28860,7 +28850,7 @@
       <c r="B33" s="12" t="s">
         <v>512</v>
       </c>
-      <c r="C33" s="54" t="s">
+      <c r="C33" s="1" t="s">
         <v>116</v>
       </c>
       <c r="D33" s="10" t="s">
@@ -28869,7 +28859,7 @@
       <c r="E33" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F33" s="53" t="s">
+      <c r="F33" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G33" s="1"/>
@@ -28881,7 +28871,7 @@
       <c r="B34" s="12" t="s">
         <v>442</v>
       </c>
-      <c r="C34" s="54" t="s">
+      <c r="C34" s="1" t="s">
         <v>443</v>
       </c>
       <c r="D34" s="10" t="s">
@@ -28890,7 +28880,7 @@
       <c r="E34" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F34" s="53" t="s">
+      <c r="F34" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G34" s="1"/>
@@ -28902,7 +28892,7 @@
       <c r="B35" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="C35" s="55" t="s">
+      <c r="C35" s="49" t="s">
         <v>109</v>
       </c>
       <c r="D35" s="10" t="s">
@@ -28911,7 +28901,7 @@
       <c r="E35" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F35" s="53" t="s">
+      <c r="F35" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G35" s="1"/>
@@ -28923,7 +28913,7 @@
       <c r="B36" s="12" t="s">
         <v>472</v>
       </c>
-      <c r="C36" s="54" t="s">
+      <c r="C36" s="1" t="s">
         <v>473</v>
       </c>
       <c r="D36" s="10" t="s">
@@ -28932,7 +28922,7 @@
       <c r="E36" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F36" s="53" t="s">
+      <c r="F36" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G36" s="1"/>
@@ -28944,7 +28934,7 @@
       <c r="B37" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="C37" s="52" t="s">
+      <c r="C37" s="3" t="s">
         <v>408</v>
       </c>
       <c r="D37" s="10" t="s">
@@ -28953,7 +28943,7 @@
       <c r="E37" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F37" s="53" t="s">
+      <c r="F37" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G37" s="1"/>
@@ -28965,7 +28955,7 @@
       <c r="B38" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="C38" s="52" t="s">
+      <c r="C38" s="3" t="s">
         <v>215</v>
       </c>
       <c r="D38" s="10" t="s">
@@ -28974,7 +28964,7 @@
       <c r="E38" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F38" s="53" t="s">
+      <c r="F38" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G38" s="1"/>
@@ -28986,7 +28976,7 @@
       <c r="B39" s="12" t="s">
         <v>464</v>
       </c>
-      <c r="C39" s="54" t="s">
+      <c r="C39" s="1" t="s">
         <v>465</v>
       </c>
       <c r="D39" s="10" t="s">
@@ -28995,7 +28985,7 @@
       <c r="E39" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F39" s="53" t="s">
+      <c r="F39" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G39" s="1"/>
@@ -29007,7 +28997,7 @@
       <c r="B40" s="12" t="s">
         <v>323</v>
       </c>
-      <c r="C40" s="52" t="s">
+      <c r="C40" s="3" t="s">
         <v>324</v>
       </c>
       <c r="D40" s="10" t="s">
@@ -29016,7 +29006,7 @@
       <c r="E40" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F40" s="53" t="s">
+      <c r="F40" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G40" s="1"/>
@@ -29028,7 +29018,7 @@
       <c r="B41" s="12" t="s">
         <v>575</v>
       </c>
-      <c r="C41" s="54" t="s">
+      <c r="C41" s="1" t="s">
         <v>404</v>
       </c>
       <c r="D41" s="10" t="s">
@@ -29037,7 +29027,7 @@
       <c r="E41" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F41" s="53" t="s">
+      <c r="F41" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G41" s="1"/>
@@ -29049,7 +29039,7 @@
       <c r="B42" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="C42" s="54" t="s">
+      <c r="C42" s="1" t="s">
         <v>183</v>
       </c>
       <c r="D42" s="10" t="s">
@@ -29058,7 +29048,7 @@
       <c r="E42" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F42" s="53" t="s">
+      <c r="F42" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G42" s="1"/>
@@ -29070,7 +29060,7 @@
       <c r="B43" s="12" t="s">
         <v>457</v>
       </c>
-      <c r="C43" s="54" t="s">
+      <c r="C43" s="1" t="s">
         <v>458</v>
       </c>
       <c r="D43" s="10" t="s">
@@ -29079,7 +29069,7 @@
       <c r="E43" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F43" s="53" t="s">
+      <c r="F43" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G43" s="1"/>
@@ -29091,7 +29081,7 @@
       <c r="B44" s="12" t="s">
         <v>277</v>
       </c>
-      <c r="C44" s="54" t="s">
+      <c r="C44" s="1" t="s">
         <v>160</v>
       </c>
       <c r="D44" s="10" t="s">
@@ -29100,7 +29090,7 @@
       <c r="E44" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F44" s="53" t="s">
+      <c r="F44" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G44" s="1"/>
@@ -29121,7 +29111,7 @@
       <c r="E45" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F45" s="53" t="s">
+      <c r="F45" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G45" s="1"/>
@@ -29142,7 +29132,7 @@
       <c r="E46" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F46" s="53" t="s">
+      <c r="F46" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G46" s="1"/>
@@ -29163,7 +29153,7 @@
       <c r="E47" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F47" s="53" t="s">
+      <c r="F47" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G47" s="1"/>
@@ -29184,7 +29174,7 @@
       <c r="E48" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F48" s="53" t="s">
+      <c r="F48" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G48" s="1"/>
@@ -29205,7 +29195,7 @@
       <c r="E49" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F49" s="53" t="s">
+      <c r="F49" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G49" s="1"/>
@@ -29226,7 +29216,7 @@
       <c r="E50" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F50" s="53" t="s">
+      <c r="F50" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G50" s="1"/>
@@ -29247,7 +29237,7 @@
       <c r="E51" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F51" s="53" t="s">
+      <c r="F51" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G51" s="1"/>
@@ -29268,7 +29258,7 @@
       <c r="E52" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F52" s="53" t="s">
+      <c r="F52" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G52" s="1"/>
@@ -29289,7 +29279,7 @@
       <c r="E53" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F53" s="53" t="s">
+      <c r="F53" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G53" s="1"/>
@@ -29310,7 +29300,7 @@
       <c r="E54" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F54" s="53" t="s">
+      <c r="F54" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G54" s="1"/>
@@ -29331,7 +29321,7 @@
       <c r="E55" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F55" s="53" t="s">
+      <c r="F55" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G55" s="1"/>
@@ -29352,7 +29342,7 @@
       <c r="E56" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F56" s="53" t="s">
+      <c r="F56" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G56" s="1"/>
@@ -29373,7 +29363,7 @@
       <c r="E57" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F57" s="53" t="s">
+      <c r="F57" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G57" s="1"/>
@@ -29394,7 +29384,7 @@
       <c r="E58" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F58" s="53" t="s">
+      <c r="F58" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G58" s="1"/>
@@ -29406,7 +29396,7 @@
       <c r="B59" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="C59" s="56" t="s">
+      <c r="C59" s="50" t="s">
         <v>91</v>
       </c>
       <c r="D59" s="10" t="s">
@@ -29415,7 +29405,7 @@
       <c r="E59" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F59" s="53" t="s">
+      <c r="F59" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G59" s="1"/>
@@ -29436,7 +29426,7 @@
       <c r="E60" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F60" s="53" t="s">
+      <c r="F60" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G60" s="1"/>
@@ -29448,7 +29438,7 @@
       <c r="B61" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="C61" s="56" t="s">
+      <c r="C61" s="50" t="s">
         <v>95</v>
       </c>
       <c r="D61" s="10" t="s">
@@ -29457,7 +29447,7 @@
       <c r="E61" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F61" s="53" t="s">
+      <c r="F61" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G61" s="1"/>
@@ -29478,7 +29468,7 @@
       <c r="E62" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F62" s="53" t="s">
+      <c r="F62" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G62" s="1"/>
@@ -29499,7 +29489,7 @@
       <c r="E63" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F63" s="53" t="s">
+      <c r="F63" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G63" s="1"/>
@@ -29520,7 +29510,7 @@
       <c r="E64" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F64" s="53" t="s">
+      <c r="F64" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G64" s="1"/>
@@ -29541,7 +29531,7 @@
       <c r="E65" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F65" s="53" t="s">
+      <c r="F65" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G65" s="1"/>
@@ -29562,7 +29552,7 @@
       <c r="E66" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F66" s="53" t="s">
+      <c r="F66" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G66" s="1"/>
@@ -29583,7 +29573,7 @@
       <c r="E67" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F67" s="53" t="s">
+      <c r="F67" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G67" s="1"/>
@@ -29604,7 +29594,7 @@
       <c r="E68" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F68" s="53" t="s">
+      <c r="F68" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G68" s="1"/>
@@ -29625,7 +29615,7 @@
       <c r="E69" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F69" s="53" t="s">
+      <c r="F69" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G69" s="1"/>
@@ -29646,7 +29636,7 @@
       <c r="E70" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F70" s="53" t="s">
+      <c r="F70" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G70" s="1"/>
@@ -29667,7 +29657,7 @@
       <c r="E71" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F71" s="53" t="s">
+      <c r="F71" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G71" s="1"/>
@@ -29688,7 +29678,7 @@
       <c r="E72" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F72" s="53" t="s">
+      <c r="F72" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G72" s="1"/>
@@ -29709,7 +29699,7 @@
       <c r="E73" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F73" s="53" t="s">
+      <c r="F73" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G73" s="1"/>
@@ -29730,7 +29720,7 @@
       <c r="E74" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F74" s="53" t="s">
+      <c r="F74" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G74" s="1"/>
@@ -29745,13 +29735,13 @@
       <c r="C75" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="D75" s="51" t="s">
+      <c r="D75" s="10" t="s">
         <v>335</v>
       </c>
       <c r="E75" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F75" s="53" t="s">
+      <c r="F75" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G75" s="1"/>
@@ -29772,7 +29762,7 @@
       <c r="E76" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F76" s="53" t="s">
+      <c r="F76" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G76" s="1"/>
@@ -29793,7 +29783,7 @@
       <c r="E77" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F77" s="53" t="s">
+      <c r="F77" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G77" s="1"/>
@@ -29814,7 +29804,7 @@
       <c r="E78" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F78" s="53" t="s">
+      <c r="F78" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G78" s="1"/>
@@ -29835,7 +29825,7 @@
       <c r="E79" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F79" s="53" t="s">
+      <c r="F79" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G79" s="1"/>
@@ -29856,7 +29846,7 @@
       <c r="E80" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F80" s="53" t="s">
+      <c r="F80" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G80" s="1"/>
@@ -29877,7 +29867,7 @@
       <c r="E81" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F81" s="53" t="s">
+      <c r="F81" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G81" s="1"/>
@@ -29898,7 +29888,7 @@
       <c r="E82" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F82" s="53" t="s">
+      <c r="F82" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G82" s="1"/>
@@ -29919,7 +29909,7 @@
       <c r="E83" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F83" s="53" t="s">
+      <c r="F83" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G83" s="1"/>
@@ -29940,7 +29930,7 @@
       <c r="E84" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F84" s="53" t="s">
+      <c r="F84" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G84" s="1"/>
@@ -29961,7 +29951,7 @@
       <c r="E85" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F85" s="53" t="s">
+      <c r="F85" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G85" s="42" t="s">
@@ -29984,7 +29974,7 @@
       <c r="E86" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F86" s="53" t="s">
+      <c r="F86" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G86" s="1"/>
@@ -30005,7 +29995,7 @@
       <c r="E87" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F87" s="53" t="s">
+      <c r="F87" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G87" s="1"/>
@@ -30026,7 +30016,7 @@
       <c r="E88" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F88" s="53" t="s">
+      <c r="F88" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G88" s="1"/>
@@ -30047,7 +30037,7 @@
       <c r="E89" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F89" s="53" t="s">
+      <c r="F89" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G89" s="1"/>
@@ -30068,7 +30058,7 @@
       <c r="E90" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F90" s="53" t="s">
+      <c r="F90" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G90" s="1"/>
@@ -30089,7 +30079,7 @@
       <c r="E91" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F91" s="53" t="s">
+      <c r="F91" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G91" s="12"/>
@@ -30110,7 +30100,7 @@
       <c r="E92" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F92" s="53" t="s">
+      <c r="F92" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G92" s="12"/>
@@ -30131,7 +30121,7 @@
       <c r="E93" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F93" s="53" t="s">
+      <c r="F93" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G93" s="1"/>
@@ -30152,7 +30142,7 @@
       <c r="E94" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F94" s="53" t="s">
+      <c r="F94" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G94" s="1"/>
@@ -30173,10 +30163,10 @@
       <c r="E95" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F95" s="53" t="s">
+      <c r="F95" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="G95" s="54"/>
+      <c r="G95" s="1"/>
     </row>
     <row r="96" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A96" s="10" t="s">
@@ -30194,7 +30184,7 @@
       <c r="E96" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F96" s="53" t="s">
+      <c r="F96" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G96" s="1"/>
@@ -30215,7 +30205,7 @@
       <c r="E97" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F97" s="53" t="s">
+      <c r="F97" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G97" s="1"/>
@@ -30236,7 +30226,7 @@
       <c r="E98" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F98" s="53" t="s">
+      <c r="F98" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G98" s="1"/>
@@ -30257,7 +30247,7 @@
       <c r="E99" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F99" s="53" t="s">
+      <c r="F99" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G99" s="1"/>
@@ -30278,7 +30268,7 @@
       <c r="E100" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F100" s="53" t="s">
+      <c r="F100" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G100" s="1"/>
@@ -30299,7 +30289,7 @@
       <c r="E101" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F101" s="53" t="s">
+      <c r="F101" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G101" s="1"/>
@@ -30320,7 +30310,7 @@
       <c r="E102" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F102" s="53" t="s">
+      <c r="F102" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G102" s="1"/>
@@ -30341,7 +30331,7 @@
       <c r="E103" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F103" s="53" t="s">
+      <c r="F103" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G103" s="1"/>
@@ -30362,7 +30352,7 @@
       <c r="E104" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F104" s="53" t="s">
+      <c r="F104" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G104" s="1"/>
@@ -30374,7 +30364,7 @@
       <c r="B105" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="C105" s="56" t="s">
+      <c r="C105" s="50" t="s">
         <v>95</v>
       </c>
       <c r="D105" s="10" t="s">
@@ -30383,7 +30373,7 @@
       <c r="E105" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F105" s="53" t="s">
+      <c r="F105" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G105" s="1"/>
@@ -30404,7 +30394,7 @@
       <c r="E106" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F106" s="53" t="s">
+      <c r="F106" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G106" s="1"/>
@@ -30425,7 +30415,7 @@
       <c r="E107" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F107" s="53" t="s">
+      <c r="F107" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G107" s="1"/>
@@ -30446,7 +30436,7 @@
       <c r="E108" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F108" s="53" t="s">
+      <c r="F108" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G108" s="1"/>
@@ -30467,7 +30457,7 @@
       <c r="E109" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F109" s="53" t="s">
+      <c r="F109" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G109" s="1"/>
@@ -30488,7 +30478,7 @@
       <c r="E110" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F110" s="53" t="s">
+      <c r="F110" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G110" s="1"/>
@@ -30509,7 +30499,7 @@
       <c r="E111" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F111" s="53" t="s">
+      <c r="F111" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G111" s="1"/>
@@ -30530,7 +30520,7 @@
       <c r="E112" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F112" s="53" t="s">
+      <c r="F112" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G112" s="1"/>
@@ -30551,7 +30541,7 @@
       <c r="E113" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F113" s="53" t="s">
+      <c r="F113" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G113" s="1"/>
@@ -30572,7 +30562,7 @@
       <c r="E114" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F114" s="53" t="s">
+      <c r="F114" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G114" s="1"/>
@@ -30587,13 +30577,13 @@
       <c r="C115" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="D115" s="51" t="s">
+      <c r="D115" s="10" t="s">
         <v>632</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F115" s="53" t="s">
+      <c r="F115" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G115" s="1"/>
@@ -30614,7 +30604,7 @@
       <c r="E116" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F116" s="53" t="s">
+      <c r="F116" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G116" s="1"/>
@@ -30635,7 +30625,7 @@
       <c r="E117" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F117" s="53" t="s">
+      <c r="F117" s="48" t="s">
         <v>12</v>
       </c>
       <c r="G117" s="1"/>
@@ -30656,7 +30646,7 @@
       <c r="E118" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F118" s="53" t="s">
+      <c r="F118" s="48" t="s">
         <v>18</v>
       </c>
       <c r="G118" s="1"/>
@@ -30675,7 +30665,7 @@
       <c r="E119" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F119" s="53"/>
+      <c r="F119" s="48"/>
       <c r="G119" s="1"/>
     </row>
     <row r="120" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
@@ -30692,7 +30682,7 @@
       <c r="E120" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F120" s="53"/>
+      <c r="F120" s="48"/>
       <c r="G120" s="1"/>
     </row>
     <row r="121" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
@@ -30709,7 +30699,7 @@
       <c r="E121" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F121" s="53"/>
+      <c r="F121" s="48"/>
       <c r="G121" s="1"/>
     </row>
     <row r="122" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
@@ -30726,7 +30716,7 @@
       <c r="E122" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F122" s="53"/>
+      <c r="F122" s="48"/>
       <c r="G122" s="1"/>
     </row>
     <row r="123" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
@@ -30736,14 +30726,14 @@
       <c r="B123" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="C123" s="56" t="s">
+      <c r="C123" s="50" t="s">
         <v>350</v>
       </c>
       <c r="D123" s="10"/>
       <c r="E123" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F123" s="53"/>
+      <c r="F123" s="48"/>
       <c r="G123" s="1"/>
     </row>
     <row r="124" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
@@ -30753,14 +30743,14 @@
       <c r="B124" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="C124" s="56" t="s">
+      <c r="C124" s="50" t="s">
         <v>350</v>
       </c>
       <c r="D124" s="10"/>
       <c r="E124" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F124" s="53"/>
+      <c r="F124" s="48"/>
       <c r="G124" s="1"/>
     </row>
     <row r="125" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
@@ -30777,7 +30767,7 @@
       <c r="E125" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F125" s="53"/>
+      <c r="F125" s="48"/>
       <c r="G125" s="1"/>
     </row>
     <row r="126" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
@@ -30794,7 +30784,7 @@
       <c r="E126" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F126" s="53"/>
+      <c r="F126" s="48"/>
       <c r="G126" s="1"/>
     </row>
     <row r="127" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
@@ -30811,7 +30801,7 @@
       <c r="E127" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F127" s="53"/>
+      <c r="F127" s="48"/>
       <c r="G127" s="1"/>
     </row>
     <row r="128" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
@@ -30828,7 +30818,7 @@
       <c r="E128" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F128" s="53"/>
+      <c r="F128" s="48"/>
       <c r="G128" s="1"/>
     </row>
     <row r="129" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
@@ -30845,7 +30835,7 @@
       <c r="E129" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F129" s="53"/>
+      <c r="F129" s="48"/>
       <c r="G129" s="1"/>
     </row>
     <row r="130" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
@@ -30862,7 +30852,7 @@
       <c r="E130" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F130" s="53"/>
+      <c r="F130" s="48"/>
       <c r="G130" s="1"/>
     </row>
     <row r="131" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
@@ -30879,7 +30869,7 @@
       <c r="E131" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F131" s="53"/>
+      <c r="F131" s="48"/>
       <c r="G131" s="1"/>
     </row>
     <row r="132" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
@@ -30896,7 +30886,7 @@
       <c r="E132" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F132" s="53"/>
+      <c r="F132" s="48"/>
       <c r="G132" s="1"/>
     </row>
     <row r="133" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
@@ -30913,7 +30903,7 @@
       <c r="E133" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F133" s="53"/>
+      <c r="F133" s="48"/>
       <c r="G133" s="1"/>
     </row>
     <row r="134" spans="1:7" ht="14.25" x14ac:dyDescent="0.2">
@@ -30930,7 +30920,7 @@
       <c r="E134" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F134" s="53"/>
+      <c r="F134" s="48"/>
       <c r="G134" s="1"/>
     </row>
   </sheetData>
